--- a/02-data/03-final-RA.xlsx
+++ b/02-data/03-final-RA.xlsx
@@ -12,7 +12,64 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="295">
+  <si>
+    <t>framework_id</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>F6</t>
+  </si>
+  <si>
+    <t>F7</t>
+  </si>
+  <si>
+    <t>F8</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>F13</t>
+  </si>
+  <si>
+    <t>F14</t>
+  </si>
+  <si>
+    <t>F15</t>
+  </si>
+  <si>
+    <t>F16</t>
+  </si>
+  <si>
+    <t>F17</t>
+  </si>
+  <si>
+    <t>F18</t>
+  </si>
   <si>
     <t>framework_name</t>
   </si>
@@ -69,63 +126,6 @@
   </si>
   <si>
     <t>Tianshou</t>
-  </si>
-  <si>
-    <t>framework_id</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>F2</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>F4</t>
-  </si>
-  <si>
-    <t>F5</t>
-  </si>
-  <si>
-    <t>F6</t>
-  </si>
-  <si>
-    <t>F7</t>
-  </si>
-  <si>
-    <t>F8</t>
-  </si>
-  <si>
-    <t>F9</t>
-  </si>
-  <si>
-    <t>F10</t>
-  </si>
-  <si>
-    <t>F11</t>
-  </si>
-  <si>
-    <t>F12</t>
-  </si>
-  <si>
-    <t>F13</t>
-  </si>
-  <si>
-    <t>F14</t>
-  </si>
-  <si>
-    <t>F15</t>
-  </si>
-  <si>
-    <t>F16</t>
-  </si>
-  <si>
-    <t>F17</t>
-  </si>
-  <si>
-    <t>F18</t>
   </si>
   <si>
     <t>component group</t>
@@ -2831,52 +2831,52 @@
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="U1" s="1"/>
@@ -2897,52 +2897,52 @@
       <c r="D2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="3" t="s">
         <v>37</v>
       </c>
       <c r="U2" s="1"/>
@@ -2953,10 +2953,10 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -31962,27 +31962,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>91</v>
       </c>
       <c r="I1" s="5"/>
@@ -32005,11 +32005,12 @@
       <c r="Z1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="5" t="str">
+        <f t="array" ref="A2">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A1)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C2" s="5" t="str">
         <f t="array" ref="C2">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A1)-1, 23)+1)</f>
@@ -32043,11 +32044,12 @@
       <c r="Z2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="5" t="str">
+        <f t="array" ref="A3">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A2)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C3" s="5" t="str">
         <f t="array" ref="C3">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A2)-1, 23)+1)</f>
@@ -32081,11 +32083,12 @@
       <c r="Z3" s="5"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="5" t="str">
+        <f t="array" ref="A4">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A3)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C4" s="5" t="str">
         <f t="array" ref="C4">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A3)-1, 23)+1)</f>
@@ -32119,11 +32122,12 @@
       <c r="Z4" s="8"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="5" t="str">
+        <f t="array" ref="A5">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A4)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C5" s="5" t="str">
         <f t="array" ref="C5">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A4)-1, 23)+1)</f>
@@ -32157,11 +32161,12 @@
       <c r="Z5" s="8"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="5" t="str">
+        <f t="array" ref="A6">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A5)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C6" s="5" t="str">
         <f t="array" ref="C6">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A5)-1, 23)+1)</f>
@@ -32195,11 +32200,12 @@
       <c r="Z6" s="8"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="5" t="str">
+        <f t="array" ref="A7">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A6)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C7" s="5" t="str">
         <f t="array" ref="C7">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A6)-1, 23)+1)</f>
@@ -32233,11 +32239,12 @@
       <c r="Z7" s="8"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="5" t="str">
+        <f t="array" ref="A8">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A7)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C8" s="5" t="str">
         <f t="array" ref="C8">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A7)-1, 23)+1)</f>
@@ -32271,11 +32278,12 @@
       <c r="Z8" s="8"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="5" t="str">
+        <f t="array" ref="A9">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A8)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C9" s="5" t="str">
         <f t="array" ref="C9">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A8)-1, 23)+1)</f>
@@ -32309,11 +32317,12 @@
       <c r="Z9" s="8"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="5" t="str">
+        <f t="array" ref="A10">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A9)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C10" s="5" t="str">
         <f t="array" ref="C10">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A9)-1, 23)+1)</f>
@@ -32348,11 +32357,12 @@
       <c r="Z10" s="8"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="5" t="str">
+        <f t="array" ref="A11">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A10)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C11" s="5" t="str">
         <f t="array" ref="C11">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A10)-1, 23)+1)</f>
@@ -32386,11 +32396,12 @@
       <c r="Z11" s="8"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="5" t="str">
+        <f t="array" ref="A12">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A11)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C12" s="5" t="str">
         <f t="array" ref="C12">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A11)-1, 23)+1)</f>
@@ -32424,11 +32435,12 @@
       <c r="Z12" s="8"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="5" t="str">
+        <f t="array" ref="A13">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A12)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C13" s="5" t="str">
         <f t="array" ref="C13">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A12)-1, 23)+1)</f>
@@ -32462,11 +32474,12 @@
       <c r="Z13" s="8"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="5" t="str">
+        <f t="array" ref="A14">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A13)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C14" s="5" t="str">
         <f t="array" ref="C14">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A13)-1, 23)+1)</f>
@@ -32500,11 +32513,12 @@
       <c r="Z14" s="8"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="5" t="str">
+        <f t="array" ref="A15">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A14)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C15" s="5" t="str">
         <f t="array" ref="C15">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A14)-1, 23)+1)</f>
@@ -32542,11 +32556,12 @@
       <c r="Z15" s="8"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="5" t="str">
+        <f t="array" ref="A16">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A15)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C16" s="5" t="str">
         <f t="array" ref="C16">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A15)-1, 23)+1)</f>
@@ -32586,11 +32601,12 @@
       <c r="Z16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="5" t="str">
+        <f t="array" ref="A17">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A16)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C17" s="5" t="str">
         <f t="array" ref="C17">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A16)-1, 23)+1)</f>
@@ -32630,11 +32646,12 @@
       <c r="Z17" s="8"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="5" t="str">
+        <f t="array" ref="A18">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A17)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C18" s="5" t="str">
         <f t="array" ref="C18">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A17)-1, 23)+1)</f>
@@ -32674,11 +32691,12 @@
       <c r="Z18" s="8"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="5" t="str">
+        <f t="array" ref="A19">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A18)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C19" s="5" t="str">
         <f t="array" ref="C19">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A18)-1, 23)+1)</f>
@@ -32712,11 +32730,12 @@
       <c r="Z19" s="8"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="5" t="str">
+        <f t="array" ref="A20">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A19)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C20" s="5" t="str">
         <f t="array" ref="C20">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A19)-1, 23)+1)</f>
@@ -32751,11 +32770,12 @@
       <c r="Z20" s="8"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="5" t="str">
+        <f t="array" ref="A21">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A20)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C21" s="5" t="str">
         <f t="array" ref="C21">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A20)-1, 23)+1)</f>
@@ -32793,11 +32813,12 @@
       <c r="Z21" s="8"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="5" t="str">
+        <f t="array" ref="A22">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A21)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C22" s="5" t="str">
         <f t="array" ref="C22">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A21)-1, 23)+1)</f>
@@ -32835,11 +32856,12 @@
       <c r="Z22" s="8"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="5" t="str">
+        <f t="array" ref="A23">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A22)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C23" s="5" t="str">
         <f t="array" ref="C23">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A22)-1, 23)+1)</f>
@@ -32877,11 +32899,12 @@
       <c r="Z23" s="8"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="5" t="str">
+        <f t="array" ref="A24">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A23)-1)/23)+1)</f>
+        <v>F1</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>1</v>
       </c>
       <c r="C24" s="5" t="str">
         <f t="array" ref="C24">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A23)-1, 23)+1)</f>
@@ -32919,11 +32942,12 @@
       <c r="Z24" s="8"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="5" t="str">
+        <f t="array" ref="A25">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A24)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C25" s="5" t="str">
         <f t="array" ref="C25">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A24)-1, 23)+1)</f>
@@ -32957,11 +32981,12 @@
       <c r="Z25" s="8"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="5" t="str">
+        <f t="array" ref="A26">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A25)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C26" s="5" t="str">
         <f t="array" ref="C26">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A25)-1, 23)+1)</f>
@@ -32995,11 +33020,12 @@
       <c r="Z26" s="8"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="5" t="str">
+        <f t="array" ref="A27">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A26)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C27" s="5" t="str">
         <f t="array" ref="C27">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A26)-1, 23)+1)</f>
@@ -33033,11 +33059,12 @@
       <c r="Z27" s="8"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="5" t="str">
+        <f t="array" ref="A28">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A27)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C28" s="5" t="str">
         <f t="array" ref="C28">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A27)-1, 23)+1)</f>
@@ -33071,11 +33098,12 @@
       <c r="Z28" s="8"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="5" t="str">
+        <f t="array" ref="A29">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A28)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C29" s="5" t="str">
         <f t="array" ref="C29">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A28)-1, 23)+1)</f>
@@ -33109,11 +33137,12 @@
       <c r="Z29" s="8"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="5" t="str">
+        <f t="array" ref="A30">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A29)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C30" s="5" t="str">
         <f t="array" ref="C30">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A29)-1, 23)+1)</f>
@@ -33147,11 +33176,12 @@
       <c r="Z30" s="8"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="5" t="str">
+        <f t="array" ref="A31">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A30)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C31" s="5" t="str">
         <f t="array" ref="C31">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A30)-1, 23)+1)</f>
@@ -33185,11 +33215,12 @@
       <c r="Z31" s="8"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="5" t="str">
+        <f t="array" ref="A32">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A31)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C32" s="5" t="str">
         <f t="array" ref="C32">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A31)-1, 23)+1)</f>
@@ -33229,11 +33260,12 @@
       <c r="Z32" s="8"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="5" t="str">
+        <f t="array" ref="A33">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A32)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C33" s="5" t="str">
         <f t="array" ref="C33">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A32)-1, 23)+1)</f>
@@ -33268,11 +33300,12 @@
       <c r="Z33" s="8"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="5" t="str">
+        <f t="array" ref="A34">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A33)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C34" s="5" t="str">
         <f t="array" ref="C34">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A33)-1, 23)+1)</f>
@@ -33306,11 +33339,12 @@
       <c r="Z34" s="8"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="5" t="str">
+        <f t="array" ref="A35">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A34)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B35" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C35" s="5" t="str">
         <f t="array" ref="C35">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A34)-1, 23)+1)</f>
@@ -33344,11 +33378,12 @@
       <c r="Z35" s="8"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="5" t="str">
+        <f t="array" ref="A36">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A35)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B36" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C36" s="5" t="str">
         <f t="array" ref="C36">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A35)-1, 23)+1)</f>
@@ -33382,11 +33417,12 @@
       <c r="Z36" s="8"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="5" t="str">
+        <f t="array" ref="A37">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A36)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B37" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C37" s="5" t="str">
         <f t="array" ref="C37">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A36)-1, 23)+1)</f>
@@ -33420,11 +33456,12 @@
       <c r="Z37" s="8"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="5" t="str">
+        <f t="array" ref="A38">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A37)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B38" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C38" s="5" t="str">
         <f t="array" ref="C38">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A37)-1, 23)+1)</f>
@@ -33462,11 +33499,12 @@
       <c r="Z38" s="8"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="5" t="str">
+        <f t="array" ref="A39">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A38)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C39" s="5" t="str">
         <f t="array" ref="C39">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A38)-1, 23)+1)</f>
@@ -33506,11 +33544,12 @@
       <c r="Z39" s="8"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="5" t="str">
+        <f t="array" ref="A40">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A39)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B40" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C40" s="5" t="str">
         <f t="array" ref="C40">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A39)-1, 23)+1)</f>
@@ -33550,11 +33589,12 @@
       <c r="Z40" s="8"/>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="5" t="str">
+        <f t="array" ref="A41">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A40)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B41" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C41" s="5" t="str">
         <f t="array" ref="C41">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A40)-1, 23)+1)</f>
@@ -33594,11 +33634,12 @@
       <c r="Z41" s="8"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="5" t="str">
+        <f t="array" ref="A42">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A41)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B42" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C42" s="5" t="str">
         <f t="array" ref="C42">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A41)-1, 23)+1)</f>
@@ -33632,11 +33673,12 @@
       <c r="Z42" s="8"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="5" t="str">
+        <f t="array" ref="A43">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A42)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C43" s="5" t="str">
         <f t="array" ref="C43">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A42)-1, 23)+1)</f>
@@ -33671,11 +33713,12 @@
       <c r="Z43" s="8"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="5" t="str">
+        <f t="array" ref="A44">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A43)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B44" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C44" s="5" t="str">
         <f t="array" ref="C44">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A43)-1, 23)+1)</f>
@@ -33715,11 +33758,12 @@
       <c r="Z44" s="8"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="5" t="str">
+        <f t="array" ref="A45">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A44)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B45" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C45" s="5" t="str">
         <f t="array" ref="C45">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A44)-1, 23)+1)</f>
@@ -33757,11 +33801,12 @@
       <c r="Z45" s="8"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="5" t="str">
+        <f t="array" ref="A46">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A45)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B46" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C46" s="5" t="str">
         <f t="array" ref="C46">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A45)-1, 23)+1)</f>
@@ -33799,11 +33844,12 @@
       <c r="Z46" s="8"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="5" t="str">
+        <f t="array" ref="A47">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A46)-1)/23)+1)</f>
+        <v>F2</v>
+      </c>
+      <c r="B47" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="C47" s="5" t="str">
         <f t="array" ref="C47">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A46)-1, 23)+1)</f>
@@ -33843,11 +33889,12 @@
       <c r="Z47" s="8"/>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="5" t="str">
+        <f t="array" ref="A48">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A47)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B48" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C48" s="5" t="str">
         <f t="array" ref="C48">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A47)-1, 23)+1)</f>
@@ -33881,11 +33928,12 @@
       <c r="Z48" s="8"/>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="5" t="str">
+        <f t="array" ref="A49">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A48)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B49" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C49" s="5" t="str">
         <f t="array" ref="C49">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A48)-1, 23)+1)</f>
@@ -33925,11 +33973,12 @@
       <c r="Z49" s="8"/>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="5" t="str">
+        <f t="array" ref="A50">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A49)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B50" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C50" s="5" t="str">
         <f t="array" ref="C50">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A49)-1, 23)+1)</f>
@@ -33963,11 +34012,12 @@
       <c r="Z50" s="8"/>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="5" t="str">
+        <f t="array" ref="A51">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A50)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B51" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C51" s="5" t="str">
         <f t="array" ref="C51">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A50)-1, 23)+1)</f>
@@ -34001,11 +34051,12 @@
       <c r="Z51" s="8"/>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="5" t="str">
+        <f t="array" ref="A52">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A51)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B52" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C52" s="5" t="str">
         <f t="array" ref="C52">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A51)-1, 23)+1)</f>
@@ -34045,11 +34096,12 @@
       <c r="Z52" s="8"/>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="5" t="str">
+        <f t="array" ref="A53">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A52)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B53" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C53" s="5" t="str">
         <f t="array" ref="C53">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A52)-1, 23)+1)</f>
@@ -34089,11 +34141,12 @@
       <c r="Z53" s="8"/>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="5" t="str">
+        <f t="array" ref="A54">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A53)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B54" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C54" s="5" t="str">
         <f t="array" ref="C54">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A53)-1, 23)+1)</f>
@@ -34127,11 +34180,12 @@
       <c r="Z54" s="8"/>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="5" t="str">
+        <f t="array" ref="A55">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A54)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B55" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C55" s="5" t="str">
         <f t="array" ref="C55">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A54)-1, 23)+1)</f>
@@ -34169,11 +34223,12 @@
       <c r="Z55" s="8"/>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="5" t="str">
+        <f t="array" ref="A56">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A55)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B56" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C56" s="5" t="str">
         <f t="array" ref="C56">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A55)-1, 23)+1)</f>
@@ -34208,11 +34263,12 @@
       <c r="Z56" s="8"/>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="5" t="str">
+        <f t="array" ref="A57">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A56)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B57" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C57" s="5" t="str">
         <f t="array" ref="C57">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A56)-1, 23)+1)</f>
@@ -34250,11 +34306,12 @@
       <c r="Z57" s="8"/>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="5" t="str">
+        <f t="array" ref="A58">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A57)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B58" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C58" s="5" t="str">
         <f t="array" ref="C58">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A57)-1, 23)+1)</f>
@@ -34292,11 +34349,12 @@
       <c r="Z58" s="8"/>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="5" t="str">
+        <f t="array" ref="A59">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A58)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B59" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C59" s="5" t="str">
         <f t="array" ref="C59">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A58)-1, 23)+1)</f>
@@ -34334,11 +34392,12 @@
       <c r="Z59" s="8"/>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="5" t="str">
+        <f t="array" ref="A60">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A59)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B60" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C60" s="5" t="str">
         <f t="array" ref="C60">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A59)-1, 23)+1)</f>
@@ -34378,11 +34437,12 @@
       <c r="Z60" s="8"/>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="5" t="str">
+        <f t="array" ref="A61">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A60)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B61" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C61" s="5" t="str">
         <f t="array" ref="C61">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A60)-1, 23)+1)</f>
@@ -34418,11 +34478,12 @@
       <c r="Z61" s="8"/>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="5" t="str">
+        <f t="array" ref="A62">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A61)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B62" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C62" s="5" t="str">
         <f t="array" ref="C62">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A61)-1, 23)+1)</f>
@@ -34460,11 +34521,12 @@
       <c r="Z62" s="8"/>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="5" t="str">
+        <f t="array" ref="A63">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A62)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B63" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C63" s="5" t="str">
         <f t="array" ref="C63">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A62)-1, 23)+1)</f>
@@ -34504,11 +34566,12 @@
       <c r="Z63" s="8"/>
     </row>
     <row r="64">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="5" t="str">
+        <f t="array" ref="A64">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A63)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B64" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C64" s="5" t="str">
         <f t="array" ref="C64">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A63)-1, 23)+1)</f>
@@ -34548,11 +34611,12 @@
       <c r="Z64" s="8"/>
     </row>
     <row r="65">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="5" t="str">
+        <f t="array" ref="A65">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A64)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B65" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C65" s="5" t="str">
         <f t="array" ref="C65">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A64)-1, 23)+1)</f>
@@ -34590,11 +34654,12 @@
       <c r="Z65" s="8"/>
     </row>
     <row r="66">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="5" t="str">
+        <f t="array" ref="A66">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A65)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B66" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C66" s="5" t="str">
         <f t="array" ref="C66">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A65)-1, 23)+1)</f>
@@ -34633,11 +34698,12 @@
       <c r="Z66" s="8"/>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="5" t="str">
+        <f t="array" ref="A67">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A66)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B67" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C67" s="5" t="str">
         <f t="array" ref="C67">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A66)-1, 23)+1)</f>
@@ -34677,11 +34743,12 @@
       <c r="Z67" s="8"/>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="5" t="str">
+        <f t="array" ref="A68">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A67)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B68" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C68" s="5" t="str">
         <f t="array" ref="C68">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A67)-1, 23)+1)</f>
@@ -34715,11 +34782,12 @@
       <c r="Z68" s="8"/>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="5" t="str">
+        <f t="array" ref="A69">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A68)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B69" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C69" s="5" t="str">
         <f t="array" ref="C69">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A68)-1, 23)+1)</f>
@@ -34757,11 +34825,12 @@
       <c r="Z69" s="8"/>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="5" t="str">
+        <f t="array" ref="A70">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A69)-1)/23)+1)</f>
+        <v>F3</v>
+      </c>
+      <c r="B70" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>3</v>
       </c>
       <c r="C70" s="5" t="str">
         <f t="array" ref="C70">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A69)-1, 23)+1)</f>
@@ -34803,11 +34872,12 @@
       <c r="Z70" s="8"/>
     </row>
     <row r="71">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="5" t="str">
+        <f t="array" ref="A71">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A70)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B71" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C71" s="5" t="str">
         <f t="array" ref="C71">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A70)-1, 23)+1)</f>
@@ -34841,11 +34911,12 @@
       <c r="Z71" s="8"/>
     </row>
     <row r="72">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="5" t="str">
+        <f t="array" ref="A72">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A71)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B72" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C72" s="5" t="str">
         <f t="array" ref="C72">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A71)-1, 23)+1)</f>
@@ -34879,11 +34950,12 @@
       <c r="Z72" s="8"/>
     </row>
     <row r="73">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="5" t="str">
+        <f t="array" ref="A73">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A72)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B73" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C73" s="5" t="str">
         <f t="array" ref="C73">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A72)-1, 23)+1)</f>
@@ -34917,11 +34989,12 @@
       <c r="Z73" s="8"/>
     </row>
     <row r="74">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="5" t="str">
+        <f t="array" ref="A74">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A73)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B74" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C74" s="5" t="str">
         <f t="array" ref="C74">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A73)-1, 23)+1)</f>
@@ -34955,11 +35028,12 @@
       <c r="Z74" s="8"/>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="5" t="str">
+        <f t="array" ref="A75">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A74)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B75" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C75" s="5" t="str">
         <f t="array" ref="C75">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A74)-1, 23)+1)</f>
@@ -34993,11 +35067,12 @@
       <c r="Z75" s="8"/>
     </row>
     <row r="76">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="5" t="str">
+        <f t="array" ref="A76">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A75)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B76" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C76" s="5" t="str">
         <f t="array" ref="C76">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A75)-1, 23)+1)</f>
@@ -35031,11 +35106,12 @@
       <c r="Z76" s="8"/>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="5" t="str">
+        <f t="array" ref="A77">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A76)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B77" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C77" s="5" t="str">
         <f t="array" ref="C77">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A76)-1, 23)+1)</f>
@@ -35069,11 +35145,12 @@
       <c r="Z77" s="8"/>
     </row>
     <row r="78">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="5" t="str">
+        <f t="array" ref="A78">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A77)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B78" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C78" s="5" t="str">
         <f t="array" ref="C78">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A77)-1, 23)+1)</f>
@@ -35107,11 +35184,12 @@
       <c r="Z78" s="8"/>
     </row>
     <row r="79">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="5" t="str">
+        <f t="array" ref="A79">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A78)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B79" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C79" s="5" t="str">
         <f t="array" ref="C79">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A78)-1, 23)+1)</f>
@@ -35146,11 +35224,12 @@
       <c r="Z79" s="8"/>
     </row>
     <row r="80">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="5" t="str">
+        <f t="array" ref="A80">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A79)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B80" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C80" s="5" t="str">
         <f t="array" ref="C80">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A79)-1, 23)+1)</f>
@@ -35184,11 +35263,12 @@
       <c r="Z80" s="8"/>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="5" t="str">
+        <f t="array" ref="A81">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A80)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B81" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C81" s="5" t="str">
         <f t="array" ref="C81">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A80)-1, 23)+1)</f>
@@ -35222,11 +35302,12 @@
       <c r="Z81" s="8"/>
     </row>
     <row r="82">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="5" t="str">
+        <f t="array" ref="A82">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A81)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B82" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C82" s="5" t="str">
         <f t="array" ref="C82">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A81)-1, 23)+1)</f>
@@ -35260,11 +35341,12 @@
       <c r="Z82" s="8"/>
     </row>
     <row r="83">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="5" t="str">
+        <f t="array" ref="A83">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A82)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B83" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C83" s="5" t="str">
         <f t="array" ref="C83">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A82)-1, 23)+1)</f>
@@ -35298,11 +35380,12 @@
       <c r="Z83" s="8"/>
     </row>
     <row r="84">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="5" t="str">
+        <f t="array" ref="A84">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A83)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B84" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C84" s="5" t="str">
         <f t="array" ref="C84">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A83)-1, 23)+1)</f>
@@ -35340,11 +35423,12 @@
       <c r="Z84" s="8"/>
     </row>
     <row r="85">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="5" t="str">
+        <f t="array" ref="A85">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A84)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B85" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C85" s="5" t="str">
         <f t="array" ref="C85">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A84)-1, 23)+1)</f>
@@ -35384,11 +35468,12 @@
       <c r="Z85" s="8"/>
     </row>
     <row r="86">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="5" t="str">
+        <f t="array" ref="A86">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A85)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B86" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C86" s="5" t="str">
         <f t="array" ref="C86">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A85)-1, 23)+1)</f>
@@ -35428,11 +35513,12 @@
       <c r="Z86" s="8"/>
     </row>
     <row r="87">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="5" t="str">
+        <f t="array" ref="A87">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A86)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B87" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C87" s="5" t="str">
         <f t="array" ref="C87">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A86)-1, 23)+1)</f>
@@ -35472,11 +35558,12 @@
       <c r="Z87" s="8"/>
     </row>
     <row r="88">
-      <c r="A88" s="11" t="s">
+      <c r="A88" s="5" t="str">
+        <f t="array" ref="A88">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A87)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B88" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C88" s="5" t="str">
         <f t="array" ref="C88">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A87)-1, 23)+1)</f>
@@ -35510,11 +35597,12 @@
       <c r="Z88" s="8"/>
     </row>
     <row r="89">
-      <c r="A89" s="11" t="s">
+      <c r="A89" s="5" t="str">
+        <f t="array" ref="A89">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A88)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B89" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C89" s="5" t="str">
         <f t="array" ref="C89">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A88)-1, 23)+1)</f>
@@ -35555,11 +35643,12 @@
       <c r="Z89" s="8"/>
     </row>
     <row r="90">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="5" t="str">
+        <f t="array" ref="A90">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A89)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B90" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C90" s="5" t="str">
         <f t="array" ref="C90">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A89)-1, 23)+1)</f>
@@ -35597,11 +35686,12 @@
       <c r="Z90" s="8"/>
     </row>
     <row r="91">
-      <c r="A91" s="11" t="s">
+      <c r="A91" s="5" t="str">
+        <f t="array" ref="A91">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A90)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B91" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C91" s="5" t="str">
         <f t="array" ref="C91">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A90)-1, 23)+1)</f>
@@ -35641,11 +35731,12 @@
       <c r="Z91" s="8"/>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="s">
+      <c r="A92" s="5" t="str">
+        <f t="array" ref="A92">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A91)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B92" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C92" s="5" t="str">
         <f t="array" ref="C92">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A91)-1, 23)+1)</f>
@@ -35683,11 +35774,12 @@
       <c r="Z92" s="8"/>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="s">
+      <c r="A93" s="5" t="str">
+        <f t="array" ref="A93">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A92)-1)/23)+1)</f>
+        <v>F4</v>
+      </c>
+      <c r="B93" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>4</v>
       </c>
       <c r="C93" s="5" t="str">
         <f t="array" ref="C93">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A92)-1, 23)+1)</f>
@@ -35727,11 +35819,12 @@
       <c r="Z93" s="8"/>
     </row>
     <row r="94">
-      <c r="A94" s="11" t="s">
+      <c r="A94" s="5" t="str">
+        <f t="array" ref="A94">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A93)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B94" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C94" s="5" t="str">
         <f t="array" ref="C94">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A93)-1, 23)+1)</f>
@@ -35765,11 +35858,12 @@
       <c r="Z94" s="8"/>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="s">
+      <c r="A95" s="5" t="str">
+        <f t="array" ref="A95">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A94)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B95" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C95" s="5" t="str">
         <f t="array" ref="C95">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A94)-1, 23)+1)</f>
@@ -35803,11 +35897,12 @@
       <c r="Z95" s="8"/>
     </row>
     <row r="96">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="5" t="str">
+        <f t="array" ref="A96">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A95)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B96" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C96" s="5" t="str">
         <f t="array" ref="C96">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A95)-1, 23)+1)</f>
@@ -35841,11 +35936,12 @@
       <c r="Z96" s="8"/>
     </row>
     <row r="97">
-      <c r="A97" s="11" t="s">
+      <c r="A97" s="5" t="str">
+        <f t="array" ref="A97">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A96)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B97" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B97" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C97" s="5" t="str">
         <f t="array" ref="C97">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A96)-1, 23)+1)</f>
@@ -35879,11 +35975,12 @@
       <c r="Z97" s="8"/>
     </row>
     <row r="98">
-      <c r="A98" s="11" t="s">
+      <c r="A98" s="5" t="str">
+        <f t="array" ref="A98">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A97)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B98" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C98" s="5" t="str">
         <f t="array" ref="C98">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A97)-1, 23)+1)</f>
@@ -35917,11 +36014,12 @@
       <c r="Z98" s="8"/>
     </row>
     <row r="99">
-      <c r="A99" s="11" t="s">
+      <c r="A99" s="5" t="str">
+        <f t="array" ref="A99">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A98)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B99" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C99" s="5" t="str">
         <f t="array" ref="C99">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A98)-1, 23)+1)</f>
@@ -35955,11 +36053,12 @@
       <c r="Z99" s="8"/>
     </row>
     <row r="100">
-      <c r="A100" s="11" t="s">
+      <c r="A100" s="5" t="str">
+        <f t="array" ref="A100">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A99)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B100" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B100" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C100" s="5" t="str">
         <f t="array" ref="C100">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A99)-1, 23)+1)</f>
@@ -35999,11 +36098,12 @@
       <c r="Z100" s="8"/>
     </row>
     <row r="101">
-      <c r="A101" s="11" t="s">
+      <c r="A101" s="5" t="str">
+        <f t="array" ref="A101">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A100)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B101" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B101" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C101" s="5" t="str">
         <f t="array" ref="C101">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A100)-1, 23)+1)</f>
@@ -36043,11 +36143,12 @@
       <c r="Z101" s="8"/>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="s">
+      <c r="A102" s="5" t="str">
+        <f t="array" ref="A102">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A101)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B102" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B102" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C102" s="5" t="str">
         <f t="array" ref="C102">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A101)-1, 23)+1)</f>
@@ -36082,11 +36183,12 @@
       <c r="Z102" s="8"/>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="s">
+      <c r="A103" s="5" t="str">
+        <f t="array" ref="A103">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A102)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B103" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B103" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C103" s="5" t="str">
         <f t="array" ref="C103">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A102)-1, 23)+1)</f>
@@ -36120,11 +36222,12 @@
       <c r="Z103" s="8"/>
     </row>
     <row r="104">
-      <c r="A104" s="11" t="s">
+      <c r="A104" s="5" t="str">
+        <f t="array" ref="A104">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A103)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B104" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B104" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C104" s="5" t="str">
         <f t="array" ref="C104">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A103)-1, 23)+1)</f>
@@ -36158,11 +36261,12 @@
       <c r="Z104" s="8"/>
     </row>
     <row r="105">
-      <c r="A105" s="11" t="s">
+      <c r="A105" s="5" t="str">
+        <f t="array" ref="A105">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A104)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B105" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B105" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C105" s="5" t="str">
         <f t="array" ref="C105">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A104)-1, 23)+1)</f>
@@ -36196,11 +36300,12 @@
       <c r="Z105" s="8"/>
     </row>
     <row r="106">
-      <c r="A106" s="11" t="s">
+      <c r="A106" s="5" t="str">
+        <f t="array" ref="A106">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A105)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B106" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B106" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C106" s="5" t="str">
         <f t="array" ref="C106">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A105)-1, 23)+1)</f>
@@ -36234,11 +36339,12 @@
       <c r="Z106" s="8"/>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="s">
+      <c r="A107" s="5" t="str">
+        <f t="array" ref="A107">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A106)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B107" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B107" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C107" s="5" t="str">
         <f t="array" ref="C107">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A106)-1, 23)+1)</f>
@@ -36276,11 +36382,12 @@
       <c r="Z107" s="8"/>
     </row>
     <row r="108">
-      <c r="A108" s="11" t="s">
+      <c r="A108" s="5" t="str">
+        <f t="array" ref="A108">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A107)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B108" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B108" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C108" s="5" t="str">
         <f t="array" ref="C108">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A107)-1, 23)+1)</f>
@@ -36318,11 +36425,12 @@
       <c r="Z108" s="8"/>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="s">
+      <c r="A109" s="5" t="str">
+        <f t="array" ref="A109">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A108)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B109" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B109" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C109" s="5" t="str">
         <f t="array" ref="C109">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A108)-1, 23)+1)</f>
@@ -36362,11 +36470,12 @@
       <c r="Z109" s="8"/>
     </row>
     <row r="110">
-      <c r="A110" s="11" t="s">
+      <c r="A110" s="5" t="str">
+        <f t="array" ref="A110">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A109)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B110" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B110" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C110" s="5" t="str">
         <f t="array" ref="C110">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A109)-1, 23)+1)</f>
@@ -36406,11 +36515,12 @@
       <c r="Z110" s="8"/>
     </row>
     <row r="111">
-      <c r="A111" s="11" t="s">
+      <c r="A111" s="5" t="str">
+        <f t="array" ref="A111">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A110)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B111" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B111" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C111" s="5" t="str">
         <f t="array" ref="C111">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A110)-1, 23)+1)</f>
@@ -36444,11 +36554,12 @@
       <c r="Z111" s="8"/>
     </row>
     <row r="112">
-      <c r="A112" s="11" t="s">
+      <c r="A112" s="5" t="str">
+        <f t="array" ref="A112">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A111)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B112" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B112" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C112" s="5" t="str">
         <f t="array" ref="C112">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A111)-1, 23)+1)</f>
@@ -36489,11 +36600,12 @@
       <c r="Z112" s="8"/>
     </row>
     <row r="113">
-      <c r="A113" s="11" t="s">
+      <c r="A113" s="5" t="str">
+        <f t="array" ref="A113">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A112)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B113" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B113" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C113" s="5" t="str">
         <f t="array" ref="C113">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A112)-1, 23)+1)</f>
@@ -36531,11 +36643,12 @@
       <c r="Z113" s="8"/>
     </row>
     <row r="114">
-      <c r="A114" s="11" t="s">
+      <c r="A114" s="5" t="str">
+        <f t="array" ref="A114">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A113)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B114" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C114" s="5" t="str">
         <f t="array" ref="C114">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A113)-1, 23)+1)</f>
@@ -36573,11 +36686,12 @@
       <c r="Z114" s="8"/>
     </row>
     <row r="115">
-      <c r="A115" s="11" t="s">
+      <c r="A115" s="5" t="str">
+        <f t="array" ref="A115">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A114)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B115" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B115" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C115" s="5" t="str">
         <f t="array" ref="C115">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A114)-1, 23)+1)</f>
@@ -36615,11 +36729,12 @@
       <c r="Z115" s="8"/>
     </row>
     <row r="116">
-      <c r="A116" s="11" t="s">
+      <c r="A116" s="5" t="str">
+        <f t="array" ref="A116">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A115)-1)/23)+1)</f>
+        <v>F5</v>
+      </c>
+      <c r="B116" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B116" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C116" s="5" t="str">
         <f t="array" ref="C116">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A115)-1, 23)+1)</f>
@@ -36653,11 +36768,12 @@
       <c r="Z116" s="8"/>
     </row>
     <row r="117">
-      <c r="A117" s="11" t="s">
+      <c r="A117" s="5" t="str">
+        <f t="array" ref="A117">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A116)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B117" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B117" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C117" s="5" t="str">
         <f t="array" ref="C117">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A116)-1, 23)+1)</f>
@@ -36691,11 +36807,12 @@
       <c r="Z117" s="8"/>
     </row>
     <row r="118">
-      <c r="A118" s="11" t="s">
+      <c r="A118" s="5" t="str">
+        <f t="array" ref="A118">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A117)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B118" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B118" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C118" s="5" t="str">
         <f t="array" ref="C118">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A117)-1, 23)+1)</f>
@@ -36729,11 +36846,12 @@
       <c r="Z118" s="8"/>
     </row>
     <row r="119">
-      <c r="A119" s="11" t="s">
+      <c r="A119" s="5" t="str">
+        <f t="array" ref="A119">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A118)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B119" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B119" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C119" s="5" t="str">
         <f t="array" ref="C119">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A118)-1, 23)+1)</f>
@@ -36767,11 +36885,12 @@
       <c r="Z119" s="8"/>
     </row>
     <row r="120">
-      <c r="A120" s="11" t="s">
+      <c r="A120" s="5" t="str">
+        <f t="array" ref="A120">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A119)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B120" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B120" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C120" s="5" t="str">
         <f t="array" ref="C120">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A119)-1, 23)+1)</f>
@@ -36805,11 +36924,12 @@
       <c r="Z120" s="8"/>
     </row>
     <row r="121">
-      <c r="A121" s="11" t="s">
+      <c r="A121" s="5" t="str">
+        <f t="array" ref="A121">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A120)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B121" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B121" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C121" s="5" t="str">
         <f t="array" ref="C121">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A120)-1, 23)+1)</f>
@@ -36843,11 +36963,12 @@
       <c r="Z121" s="8"/>
     </row>
     <row r="122">
-      <c r="A122" s="11" t="s">
+      <c r="A122" s="5" t="str">
+        <f t="array" ref="A122">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A121)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B122" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B122" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C122" s="5" t="str">
         <f t="array" ref="C122">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A121)-1, 23)+1)</f>
@@ -36881,11 +37002,12 @@
       <c r="Z122" s="8"/>
     </row>
     <row r="123">
-      <c r="A123" s="11" t="s">
+      <c r="A123" s="5" t="str">
+        <f t="array" ref="A123">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A122)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B123" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B123" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C123" s="5" t="str">
         <f t="array" ref="C123">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A122)-1, 23)+1)</f>
@@ -36919,11 +37041,12 @@
       <c r="Z123" s="8"/>
     </row>
     <row r="124">
-      <c r="A124" s="11" t="s">
+      <c r="A124" s="5" t="str">
+        <f t="array" ref="A124">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A123)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B124" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B124" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C124" s="5" t="str">
         <f t="array" ref="C124">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A123)-1, 23)+1)</f>
@@ -36957,11 +37080,12 @@
       <c r="Z124" s="8"/>
     </row>
     <row r="125">
-      <c r="A125" s="11" t="s">
+      <c r="A125" s="5" t="str">
+        <f t="array" ref="A125">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A124)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B125" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B125" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C125" s="5" t="str">
         <f t="array" ref="C125">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A124)-1, 23)+1)</f>
@@ -36996,11 +37120,12 @@
       <c r="Z125" s="8"/>
     </row>
     <row r="126">
-      <c r="A126" s="11" t="s">
+      <c r="A126" s="5" t="str">
+        <f t="array" ref="A126">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A125)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B126" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B126" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C126" s="5" t="str">
         <f t="array" ref="C126">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A125)-1, 23)+1)</f>
@@ -37034,11 +37159,12 @@
       <c r="Z126" s="8"/>
     </row>
     <row r="127">
-      <c r="A127" s="11" t="s">
+      <c r="A127" s="5" t="str">
+        <f t="array" ref="A127">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A126)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B127" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B127" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C127" s="5" t="str">
         <f t="array" ref="C127">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A126)-1, 23)+1)</f>
@@ -37072,11 +37198,12 @@
       <c r="Z127" s="8"/>
     </row>
     <row r="128">
-      <c r="A128" s="11" t="s">
+      <c r="A128" s="5" t="str">
+        <f t="array" ref="A128">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A127)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B128" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B128" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C128" s="5" t="str">
         <f t="array" ref="C128">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A127)-1, 23)+1)</f>
@@ -37110,11 +37237,12 @@
       <c r="Z128" s="8"/>
     </row>
     <row r="129">
-      <c r="A129" s="11" t="s">
+      <c r="A129" s="5" t="str">
+        <f t="array" ref="A129">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A128)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B129" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B129" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C129" s="5" t="str">
         <f t="array" ref="C129">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A128)-1, 23)+1)</f>
@@ -37148,11 +37276,12 @@
       <c r="Z129" s="8"/>
     </row>
     <row r="130">
-      <c r="A130" s="11" t="s">
+      <c r="A130" s="5" t="str">
+        <f t="array" ref="A130">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A129)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B130" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B130" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C130" s="5" t="str">
         <f t="array" ref="C130">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A129)-1, 23)+1)</f>
@@ -37192,11 +37321,12 @@
       <c r="Z130" s="8"/>
     </row>
     <row r="131">
-      <c r="A131" s="11" t="s">
+      <c r="A131" s="5" t="str">
+        <f t="array" ref="A131">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A130)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B131" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B131" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C131" s="5" t="str">
         <f t="array" ref="C131">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A130)-1, 23)+1)</f>
@@ -37236,11 +37366,12 @@
       <c r="Z131" s="8"/>
     </row>
     <row r="132">
-      <c r="A132" s="11" t="s">
+      <c r="A132" s="5" t="str">
+        <f t="array" ref="A132">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A131)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B132" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B132" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C132" s="5" t="str">
         <f t="array" ref="C132">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A131)-1, 23)+1)</f>
@@ -37280,11 +37411,12 @@
       <c r="Z132" s="8"/>
     </row>
     <row r="133">
-      <c r="A133" s="11" t="s">
+      <c r="A133" s="5" t="str">
+        <f t="array" ref="A133">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A132)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B133" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B133" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C133" s="5" t="str">
         <f t="array" ref="C133">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A132)-1, 23)+1)</f>
@@ -37324,11 +37456,12 @@
       <c r="Z133" s="8"/>
     </row>
     <row r="134">
-      <c r="A134" s="11" t="s">
+      <c r="A134" s="5" t="str">
+        <f t="array" ref="A134">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A133)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B134" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B134" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C134" s="5" t="str">
         <f t="array" ref="C134">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A133)-1, 23)+1)</f>
@@ -37362,11 +37495,12 @@
       <c r="Z134" s="8"/>
     </row>
     <row r="135">
-      <c r="A135" s="11" t="s">
+      <c r="A135" s="5" t="str">
+        <f t="array" ref="A135">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A134)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B135" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B135" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C135" s="5" t="str">
         <f t="array" ref="C135">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A134)-1, 23)+1)</f>
@@ -37401,11 +37535,12 @@
       <c r="Z135" s="8"/>
     </row>
     <row r="136">
-      <c r="A136" s="11" t="s">
+      <c r="A136" s="5" t="str">
+        <f t="array" ref="A136">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A135)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B136" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B136" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C136" s="5" t="str">
         <f t="array" ref="C136">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A135)-1, 23)+1)</f>
@@ -37445,11 +37580,12 @@
       <c r="Z136" s="8"/>
     </row>
     <row r="137">
-      <c r="A137" s="11" t="s">
+      <c r="A137" s="5" t="str">
+        <f t="array" ref="A137">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A136)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B137" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B137" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C137" s="5" t="str">
         <f t="array" ref="C137">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A136)-1, 23)+1)</f>
@@ -37483,11 +37619,12 @@
       <c r="Z137" s="8"/>
     </row>
     <row r="138">
-      <c r="A138" s="11" t="s">
+      <c r="A138" s="5" t="str">
+        <f t="array" ref="A138">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A137)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B138" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B138" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C138" s="5" t="str">
         <f t="array" ref="C138">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A137)-1, 23)+1)</f>
@@ -37525,11 +37662,12 @@
       <c r="Z138" s="8"/>
     </row>
     <row r="139">
-      <c r="A139" s="11" t="s">
+      <c r="A139" s="5" t="str">
+        <f t="array" ref="A139">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A138)-1)/23)+1)</f>
+        <v>F6</v>
+      </c>
+      <c r="B139" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B139" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="C139" s="5" t="str">
         <f t="array" ref="C139">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A138)-1, 23)+1)</f>
@@ -37563,11 +37701,12 @@
       <c r="Z139" s="8"/>
     </row>
     <row r="140">
-      <c r="A140" s="11" t="s">
+      <c r="A140" s="5" t="str">
+        <f t="array" ref="A140">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A139)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B140" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B140" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C140" s="5" t="str">
         <f t="array" ref="C140">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A139)-1, 23)+1)</f>
@@ -37601,11 +37740,12 @@
       <c r="Z140" s="8"/>
     </row>
     <row r="141">
-      <c r="A141" s="11" t="s">
+      <c r="A141" s="5" t="str">
+        <f t="array" ref="A141">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A140)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B141" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B141" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C141" s="5" t="str">
         <f t="array" ref="C141">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A140)-1, 23)+1)</f>
@@ -37639,11 +37779,12 @@
       <c r="Z141" s="8"/>
     </row>
     <row r="142">
-      <c r="A142" s="11" t="s">
+      <c r="A142" s="5" t="str">
+        <f t="array" ref="A142">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A141)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B142" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B142" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C142" s="5" t="str">
         <f t="array" ref="C142">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A141)-1, 23)+1)</f>
@@ -37677,11 +37818,12 @@
       <c r="Z142" s="8"/>
     </row>
     <row r="143">
-      <c r="A143" s="11" t="s">
+      <c r="A143" s="5" t="str">
+        <f t="array" ref="A143">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A142)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B143" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B143" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C143" s="5" t="str">
         <f t="array" ref="C143">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A142)-1, 23)+1)</f>
@@ -37715,11 +37857,12 @@
       <c r="Z143" s="8"/>
     </row>
     <row r="144">
-      <c r="A144" s="11" t="s">
+      <c r="A144" s="5" t="str">
+        <f t="array" ref="A144">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A143)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B144" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B144" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C144" s="5" t="str">
         <f t="array" ref="C144">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A143)-1, 23)+1)</f>
@@ -37753,11 +37896,12 @@
       <c r="Z144" s="8"/>
     </row>
     <row r="145">
-      <c r="A145" s="11" t="s">
+      <c r="A145" s="5" t="str">
+        <f t="array" ref="A145">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A144)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B145" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B145" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C145" s="5" t="str">
         <f t="array" ref="C145">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A144)-1, 23)+1)</f>
@@ -37791,11 +37935,12 @@
       <c r="Z145" s="8"/>
     </row>
     <row r="146">
-      <c r="A146" s="11" t="s">
+      <c r="A146" s="5" t="str">
+        <f t="array" ref="A146">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A145)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B146" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B146" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C146" s="5" t="str">
         <f t="array" ref="C146">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A145)-1, 23)+1)</f>
@@ -37829,11 +37974,12 @@
       <c r="Z146" s="8"/>
     </row>
     <row r="147">
-      <c r="A147" s="11" t="s">
+      <c r="A147" s="5" t="str">
+        <f t="array" ref="A147">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A146)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B147" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B147" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C147" s="5" t="str">
         <f t="array" ref="C147">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A146)-1, 23)+1)</f>
@@ -37867,11 +38013,12 @@
       <c r="Z147" s="8"/>
     </row>
     <row r="148">
-      <c r="A148" s="11" t="s">
+      <c r="A148" s="5" t="str">
+        <f t="array" ref="A148">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A147)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B148" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B148" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C148" s="5" t="str">
         <f t="array" ref="C148">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A147)-1, 23)+1)</f>
@@ -37906,11 +38053,12 @@
       <c r="Z148" s="8"/>
     </row>
     <row r="149">
-      <c r="A149" s="11" t="s">
+      <c r="A149" s="5" t="str">
+        <f t="array" ref="A149">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A148)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B149" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B149" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C149" s="5" t="str">
         <f t="array" ref="C149">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A148)-1, 23)+1)</f>
@@ -37944,11 +38092,12 @@
       <c r="Z149" s="8"/>
     </row>
     <row r="150">
-      <c r="A150" s="11" t="s">
+      <c r="A150" s="5" t="str">
+        <f t="array" ref="A150">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A149)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B150" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B150" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C150" s="5" t="str">
         <f t="array" ref="C150">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A149)-1, 23)+1)</f>
@@ -37982,11 +38131,12 @@
       <c r="Z150" s="8"/>
     </row>
     <row r="151">
-      <c r="A151" s="11" t="s">
+      <c r="A151" s="5" t="str">
+        <f t="array" ref="A151">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A150)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B151" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B151" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C151" s="5" t="str">
         <f t="array" ref="C151">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A150)-1, 23)+1)</f>
@@ -38020,11 +38170,12 @@
       <c r="Z151" s="8"/>
     </row>
     <row r="152">
-      <c r="A152" s="11" t="s">
+      <c r="A152" s="5" t="str">
+        <f t="array" ref="A152">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A151)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B152" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B152" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C152" s="5" t="str">
         <f t="array" ref="C152">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A151)-1, 23)+1)</f>
@@ -38058,11 +38209,12 @@
       <c r="Z152" s="8"/>
     </row>
     <row r="153">
-      <c r="A153" s="11" t="s">
+      <c r="A153" s="5" t="str">
+        <f t="array" ref="A153">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A152)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B153" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B153" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C153" s="5" t="str">
         <f t="array" ref="C153">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A152)-1, 23)+1)</f>
@@ -38100,11 +38252,12 @@
       <c r="Z153" s="8"/>
     </row>
     <row r="154">
-      <c r="A154" s="11" t="s">
+      <c r="A154" s="5" t="str">
+        <f t="array" ref="A154">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A153)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B154" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B154" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C154" s="5" t="str">
         <f t="array" ref="C154">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A153)-1, 23)+1)</f>
@@ -38144,11 +38297,12 @@
       <c r="Z154" s="8"/>
     </row>
     <row r="155">
-      <c r="A155" s="11" t="s">
+      <c r="A155" s="5" t="str">
+        <f t="array" ref="A155">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A154)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B155" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B155" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C155" s="5" t="str">
         <f t="array" ref="C155">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A154)-1, 23)+1)</f>
@@ -38188,11 +38342,12 @@
       <c r="Z155" s="8"/>
     </row>
     <row r="156">
-      <c r="A156" s="11" t="s">
+      <c r="A156" s="5" t="str">
+        <f t="array" ref="A156">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A155)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B156" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B156" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C156" s="5" t="str">
         <f t="array" ref="C156">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A155)-1, 23)+1)</f>
@@ -38232,11 +38387,12 @@
       <c r="Z156" s="8"/>
     </row>
     <row r="157">
-      <c r="A157" s="11" t="s">
+      <c r="A157" s="5" t="str">
+        <f t="array" ref="A157">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A156)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B157" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B157" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C157" s="5" t="str">
         <f t="array" ref="C157">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A156)-1, 23)+1)</f>
@@ -38270,11 +38426,12 @@
       <c r="Z157" s="8"/>
     </row>
     <row r="158">
-      <c r="A158" s="11" t="s">
+      <c r="A158" s="5" t="str">
+        <f t="array" ref="A158">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A157)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B158" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B158" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C158" s="5" t="str">
         <f t="array" ref="C158">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A157)-1, 23)+1)</f>
@@ -38309,11 +38466,12 @@
       <c r="Z158" s="8"/>
     </row>
     <row r="159">
-      <c r="A159" s="11" t="s">
+      <c r="A159" s="5" t="str">
+        <f t="array" ref="A159">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A158)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B159" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B159" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C159" s="5" t="str">
         <f t="array" ref="C159">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A158)-1, 23)+1)</f>
@@ -38351,11 +38509,12 @@
       <c r="Z159" s="8"/>
     </row>
     <row r="160">
-      <c r="A160" s="11" t="s">
+      <c r="A160" s="5" t="str">
+        <f t="array" ref="A160">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A159)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B160" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B160" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C160" s="5" t="str">
         <f t="array" ref="C160">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A159)-1, 23)+1)</f>
@@ -38393,11 +38552,12 @@
       <c r="Z160" s="8"/>
     </row>
     <row r="161">
-      <c r="A161" s="11" t="s">
+      <c r="A161" s="5" t="str">
+        <f t="array" ref="A161">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A160)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B161" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B161" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C161" s="5" t="str">
         <f t="array" ref="C161">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A160)-1, 23)+1)</f>
@@ -38435,11 +38595,12 @@
       <c r="Z161" s="8"/>
     </row>
     <row r="162">
-      <c r="A162" s="11" t="s">
+      <c r="A162" s="5" t="str">
+        <f t="array" ref="A162">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A161)-1)/23)+1)</f>
+        <v>F7</v>
+      </c>
+      <c r="B162" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B162" s="11" t="s">
-        <v>7</v>
       </c>
       <c r="C162" s="5" t="str">
         <f t="array" ref="C162">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A161)-1, 23)+1)</f>
@@ -38473,11 +38634,12 @@
       <c r="Z162" s="8"/>
     </row>
     <row r="163">
-      <c r="A163" s="11" t="s">
+      <c r="A163" s="5" t="str">
+        <f t="array" ref="A163">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A162)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B163" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B163" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C163" s="5" t="str">
         <f t="array" ref="C163">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A162)-1, 23)+1)</f>
@@ -38511,11 +38673,12 @@
       <c r="Z163" s="8"/>
     </row>
     <row r="164">
-      <c r="A164" s="11" t="s">
+      <c r="A164" s="5" t="str">
+        <f t="array" ref="A164">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A163)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B164" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B164" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C164" s="5" t="str">
         <f t="array" ref="C164">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A163)-1, 23)+1)</f>
@@ -38549,11 +38712,12 @@
       <c r="Z164" s="8"/>
     </row>
     <row r="165">
-      <c r="A165" s="11" t="s">
+      <c r="A165" s="5" t="str">
+        <f t="array" ref="A165">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A164)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B165" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B165" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C165" s="5" t="str">
         <f t="array" ref="C165">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A164)-1, 23)+1)</f>
@@ -38587,11 +38751,12 @@
       <c r="Z165" s="8"/>
     </row>
     <row r="166">
-      <c r="A166" s="11" t="s">
+      <c r="A166" s="5" t="str">
+        <f t="array" ref="A166">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A165)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B166" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B166" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C166" s="5" t="str">
         <f t="array" ref="C166">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A165)-1, 23)+1)</f>
@@ -38625,11 +38790,12 @@
       <c r="Z166" s="8"/>
     </row>
     <row r="167">
-      <c r="A167" s="11" t="s">
+      <c r="A167" s="5" t="str">
+        <f t="array" ref="A167">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A166)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B167" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B167" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C167" s="5" t="str">
         <f t="array" ref="C167">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A166)-1, 23)+1)</f>
@@ -38663,11 +38829,12 @@
       <c r="Z167" s="8"/>
     </row>
     <row r="168">
-      <c r="A168" s="11" t="s">
+      <c r="A168" s="5" t="str">
+        <f t="array" ref="A168">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A167)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B168" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B168" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C168" s="5" t="str">
         <f t="array" ref="C168">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A167)-1, 23)+1)</f>
@@ -38701,11 +38868,12 @@
       <c r="Z168" s="8"/>
     </row>
     <row r="169">
-      <c r="A169" s="11" t="s">
+      <c r="A169" s="5" t="str">
+        <f t="array" ref="A169">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A168)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B169" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B169" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C169" s="5" t="str">
         <f t="array" ref="C169">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A168)-1, 23)+1)</f>
@@ -38739,11 +38907,12 @@
       <c r="Z169" s="8"/>
     </row>
     <row r="170">
-      <c r="A170" s="11" t="s">
+      <c r="A170" s="5" t="str">
+        <f t="array" ref="A170">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A169)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B170" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B170" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C170" s="5" t="str">
         <f t="array" ref="C170">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A169)-1, 23)+1)</f>
@@ -38777,11 +38946,12 @@
       <c r="Z170" s="8"/>
     </row>
     <row r="171">
-      <c r="A171" s="11" t="s">
+      <c r="A171" s="5" t="str">
+        <f t="array" ref="A171">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A170)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B171" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B171" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C171" s="5" t="str">
         <f t="array" ref="C171">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A170)-1, 23)+1)</f>
@@ -38816,11 +38986,12 @@
       <c r="Z171" s="8"/>
     </row>
     <row r="172">
-      <c r="A172" s="11" t="s">
+      <c r="A172" s="5" t="str">
+        <f t="array" ref="A172">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A171)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B172" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B172" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C172" s="5" t="str">
         <f t="array" ref="C172">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A171)-1, 23)+1)</f>
@@ -38854,11 +39025,12 @@
       <c r="Z172" s="8"/>
     </row>
     <row r="173">
-      <c r="A173" s="11" t="s">
+      <c r="A173" s="5" t="str">
+        <f t="array" ref="A173">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A172)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B173" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B173" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C173" s="5" t="str">
         <f t="array" ref="C173">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A172)-1, 23)+1)</f>
@@ -38892,11 +39064,12 @@
       <c r="Z173" s="8"/>
     </row>
     <row r="174">
-      <c r="A174" s="11" t="s">
+      <c r="A174" s="5" t="str">
+        <f t="array" ref="A174">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A173)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B174" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B174" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C174" s="5" t="str">
         <f t="array" ref="C174">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A173)-1, 23)+1)</f>
@@ -38930,11 +39103,12 @@
       <c r="Z174" s="8"/>
     </row>
     <row r="175">
-      <c r="A175" s="11" t="s">
+      <c r="A175" s="5" t="str">
+        <f t="array" ref="A175">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A174)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B175" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B175" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C175" s="5" t="str">
         <f t="array" ref="C175">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A174)-1, 23)+1)</f>
@@ -38968,11 +39142,12 @@
       <c r="Z175" s="8"/>
     </row>
     <row r="176">
-      <c r="A176" s="11" t="s">
+      <c r="A176" s="5" t="str">
+        <f t="array" ref="A176">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A175)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B176" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B176" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C176" s="5" t="str">
         <f t="array" ref="C176">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A175)-1, 23)+1)</f>
@@ -39010,11 +39185,12 @@
       <c r="Z176" s="8"/>
     </row>
     <row r="177">
-      <c r="A177" s="11" t="s">
+      <c r="A177" s="5" t="str">
+        <f t="array" ref="A177">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A176)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B177" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B177" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C177" s="5" t="str">
         <f t="array" ref="C177">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A176)-1, 23)+1)</f>
@@ -39054,11 +39230,12 @@
       <c r="Z177" s="8"/>
     </row>
     <row r="178">
-      <c r="A178" s="11" t="s">
+      <c r="A178" s="5" t="str">
+        <f t="array" ref="A178">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A177)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B178" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B178" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C178" s="5" t="str">
         <f t="array" ref="C178">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A177)-1, 23)+1)</f>
@@ -39098,11 +39275,12 @@
       <c r="Z178" s="8"/>
     </row>
     <row r="179">
-      <c r="A179" s="11" t="s">
+      <c r="A179" s="5" t="str">
+        <f t="array" ref="A179">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A178)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B179" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B179" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C179" s="5" t="str">
         <f t="array" ref="C179">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A178)-1, 23)+1)</f>
@@ -39142,11 +39320,12 @@
       <c r="Z179" s="8"/>
     </row>
     <row r="180">
-      <c r="A180" s="11" t="s">
+      <c r="A180" s="5" t="str">
+        <f t="array" ref="A180">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A179)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B180" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B180" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C180" s="5" t="str">
         <f t="array" ref="C180">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A179)-1, 23)+1)</f>
@@ -39180,11 +39359,12 @@
       <c r="Z180" s="8"/>
     </row>
     <row r="181">
-      <c r="A181" s="11" t="s">
+      <c r="A181" s="5" t="str">
+        <f t="array" ref="A181">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A180)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B181" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B181" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C181" s="5" t="str">
         <f t="array" ref="C181">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A180)-1, 23)+1)</f>
@@ -39225,11 +39405,12 @@
       <c r="Z181" s="8"/>
     </row>
     <row r="182">
-      <c r="A182" s="11" t="s">
+      <c r="A182" s="5" t="str">
+        <f t="array" ref="A182">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A181)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B182" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B182" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C182" s="5" t="str">
         <f t="array" ref="C182">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A181)-1, 23)+1)</f>
@@ -39267,11 +39448,12 @@
       <c r="Z182" s="8"/>
     </row>
     <row r="183">
-      <c r="A183" s="11" t="s">
+      <c r="A183" s="5" t="str">
+        <f t="array" ref="A183">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A182)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B183" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B183" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C183" s="5" t="str">
         <f t="array" ref="C183">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A182)-1, 23)+1)</f>
@@ -39309,11 +39491,12 @@
       <c r="Z183" s="8"/>
     </row>
     <row r="184">
-      <c r="A184" s="11" t="s">
+      <c r="A184" s="5" t="str">
+        <f t="array" ref="A184">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A183)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B184" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B184" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C184" s="5" t="str">
         <f t="array" ref="C184">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A183)-1, 23)+1)</f>
@@ -39351,11 +39534,12 @@
       <c r="Z184" s="8"/>
     </row>
     <row r="185">
-      <c r="A185" s="11" t="s">
+      <c r="A185" s="5" t="str">
+        <f t="array" ref="A185">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A184)-1)/23)+1)</f>
+        <v>F8</v>
+      </c>
+      <c r="B185" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="B185" s="11" t="s">
-        <v>8</v>
       </c>
       <c r="C185" s="5" t="str">
         <f t="array" ref="C185">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A184)-1, 23)+1)</f>
@@ -39389,11 +39573,12 @@
       <c r="Z185" s="8"/>
     </row>
     <row r="186">
-      <c r="A186" s="11" t="s">
+      <c r="A186" s="5" t="str">
+        <f t="array" ref="A186">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A185)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B186" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B186" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C186" s="5" t="str">
         <f t="array" ref="C186">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A185)-1, 23)+1)</f>
@@ -39427,11 +39612,12 @@
       <c r="Z186" s="8"/>
     </row>
     <row r="187">
-      <c r="A187" s="11" t="s">
+      <c r="A187" s="5" t="str">
+        <f t="array" ref="A187">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A186)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B187" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B187" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C187" s="5" t="str">
         <f t="array" ref="C187">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A186)-1, 23)+1)</f>
@@ -39465,11 +39651,12 @@
       <c r="Z187" s="8"/>
     </row>
     <row r="188">
-      <c r="A188" s="11" t="s">
+      <c r="A188" s="5" t="str">
+        <f t="array" ref="A188">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A187)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B188" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B188" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C188" s="5" t="str">
         <f t="array" ref="C188">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A187)-1, 23)+1)</f>
@@ -39503,11 +39690,12 @@
       <c r="Z188" s="8"/>
     </row>
     <row r="189">
-      <c r="A189" s="11" t="s">
+      <c r="A189" s="5" t="str">
+        <f t="array" ref="A189">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A188)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B189" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B189" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C189" s="5" t="str">
         <f t="array" ref="C189">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A188)-1, 23)+1)</f>
@@ -39541,11 +39729,12 @@
       <c r="Z189" s="8"/>
     </row>
     <row r="190">
-      <c r="A190" s="11" t="s">
+      <c r="A190" s="5" t="str">
+        <f t="array" ref="A190">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A189)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B190" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B190" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C190" s="5" t="str">
         <f t="array" ref="C190">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A189)-1, 23)+1)</f>
@@ -39579,11 +39768,12 @@
       <c r="Z190" s="8"/>
     </row>
     <row r="191">
-      <c r="A191" s="11" t="s">
+      <c r="A191" s="5" t="str">
+        <f t="array" ref="A191">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A190)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B191" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B191" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C191" s="5" t="str">
         <f t="array" ref="C191">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A190)-1, 23)+1)</f>
@@ -39617,11 +39807,12 @@
       <c r="Z191" s="8"/>
     </row>
     <row r="192">
-      <c r="A192" s="11" t="s">
+      <c r="A192" s="5" t="str">
+        <f t="array" ref="A192">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A191)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B192" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B192" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C192" s="5" t="str">
         <f t="array" ref="C192">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A191)-1, 23)+1)</f>
@@ -39655,11 +39846,12 @@
       <c r="Z192" s="8"/>
     </row>
     <row r="193">
-      <c r="A193" s="11" t="s">
+      <c r="A193" s="5" t="str">
+        <f t="array" ref="A193">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A192)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B193" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B193" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C193" s="5" t="str">
         <f t="array" ref="C193">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A192)-1, 23)+1)</f>
@@ -39693,11 +39885,12 @@
       <c r="Z193" s="8"/>
     </row>
     <row r="194">
-      <c r="A194" s="11" t="s">
+      <c r="A194" s="5" t="str">
+        <f t="array" ref="A194">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A193)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B194" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B194" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C194" s="5" t="str">
         <f t="array" ref="C194">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A193)-1, 23)+1)</f>
@@ -39732,11 +39925,12 @@
       <c r="Z194" s="8"/>
     </row>
     <row r="195">
-      <c r="A195" s="11" t="s">
+      <c r="A195" s="5" t="str">
+        <f t="array" ref="A195">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A194)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B195" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B195" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C195" s="5" t="str">
         <f t="array" ref="C195">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A194)-1, 23)+1)</f>
@@ -39770,11 +39964,12 @@
       <c r="Z195" s="8"/>
     </row>
     <row r="196">
-      <c r="A196" s="11" t="s">
+      <c r="A196" s="5" t="str">
+        <f t="array" ref="A196">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A195)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B196" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B196" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C196" s="5" t="str">
         <f t="array" ref="C196">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A195)-1, 23)+1)</f>
@@ -39808,11 +40003,12 @@
       <c r="Z196" s="8"/>
     </row>
     <row r="197">
-      <c r="A197" s="11" t="s">
+      <c r="A197" s="5" t="str">
+        <f t="array" ref="A197">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A196)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B197" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B197" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C197" s="5" t="str">
         <f t="array" ref="C197">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A196)-1, 23)+1)</f>
@@ -39846,11 +40042,12 @@
       <c r="Z197" s="8"/>
     </row>
     <row r="198">
-      <c r="A198" s="11" t="s">
+      <c r="A198" s="5" t="str">
+        <f t="array" ref="A198">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A197)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B198" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B198" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C198" s="5" t="str">
         <f t="array" ref="C198">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A197)-1, 23)+1)</f>
@@ -39884,11 +40081,12 @@
       <c r="Z198" s="8"/>
     </row>
     <row r="199">
-      <c r="A199" s="11" t="s">
+      <c r="A199" s="5" t="str">
+        <f t="array" ref="A199">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A198)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B199" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B199" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C199" s="5" t="str">
         <f t="array" ref="C199">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A198)-1, 23)+1)</f>
@@ -39926,11 +40124,12 @@
       <c r="Z199" s="8"/>
     </row>
     <row r="200">
-      <c r="A200" s="11" t="s">
+      <c r="A200" s="5" t="str">
+        <f t="array" ref="A200">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A199)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B200" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B200" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C200" s="5" t="str">
         <f t="array" ref="C200">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A199)-1, 23)+1)</f>
@@ -39970,11 +40169,12 @@
       <c r="Z200" s="8"/>
     </row>
     <row r="201">
-      <c r="A201" s="11" t="s">
+      <c r="A201" s="5" t="str">
+        <f t="array" ref="A201">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A200)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B201" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B201" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C201" s="5" t="str">
         <f t="array" ref="C201">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A200)-1, 23)+1)</f>
@@ -40014,11 +40214,12 @@
       <c r="Z201" s="8"/>
     </row>
     <row r="202">
-      <c r="A202" s="11" t="s">
+      <c r="A202" s="5" t="str">
+        <f t="array" ref="A202">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A201)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B202" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B202" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C202" s="5" t="str">
         <f t="array" ref="C202">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A201)-1, 23)+1)</f>
@@ -40052,11 +40253,12 @@
       <c r="Z202" s="8"/>
     </row>
     <row r="203">
-      <c r="A203" s="11" t="s">
+      <c r="A203" s="5" t="str">
+        <f t="array" ref="A203">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A202)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B203" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B203" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C203" s="5" t="str">
         <f t="array" ref="C203">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A202)-1, 23)+1)</f>
@@ -40094,11 +40296,12 @@
       <c r="Z203" s="8"/>
     </row>
     <row r="204">
-      <c r="A204" s="11" t="s">
+      <c r="A204" s="5" t="str">
+        <f t="array" ref="A204">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A203)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B204" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B204" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C204" s="5" t="str">
         <f t="array" ref="C204">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A203)-1, 23)+1)</f>
@@ -40133,11 +40336,12 @@
       <c r="Z204" s="8"/>
     </row>
     <row r="205">
-      <c r="A205" s="11" t="s">
+      <c r="A205" s="5" t="str">
+        <f t="array" ref="A205">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A204)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B205" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B205" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C205" s="5" t="str">
         <f t="array" ref="C205">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A204)-1, 23)+1)</f>
@@ -40175,11 +40379,12 @@
       <c r="Z205" s="8"/>
     </row>
     <row r="206">
-      <c r="A206" s="11" t="s">
+      <c r="A206" s="5" t="str">
+        <f t="array" ref="A206">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A205)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B206" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B206" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C206" s="5" t="str">
         <f t="array" ref="C206">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A205)-1, 23)+1)</f>
@@ -40213,11 +40418,12 @@
       <c r="Z206" s="8"/>
     </row>
     <row r="207">
-      <c r="A207" s="11" t="s">
+      <c r="A207" s="5" t="str">
+        <f t="array" ref="A207">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A206)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B207" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B207" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C207" s="5" t="str">
         <f t="array" ref="C207">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A206)-1, 23)+1)</f>
@@ -40255,11 +40461,12 @@
       <c r="Z207" s="8"/>
     </row>
     <row r="208">
-      <c r="A208" s="11" t="s">
+      <c r="A208" s="5" t="str">
+        <f t="array" ref="A208">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A207)-1)/23)+1)</f>
+        <v>F9</v>
+      </c>
+      <c r="B208" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B208" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="C208" s="5" t="str">
         <f t="array" ref="C208">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A207)-1, 23)+1)</f>
@@ -40293,11 +40500,12 @@
       <c r="Z208" s="8"/>
     </row>
     <row r="209">
-      <c r="A209" s="11" t="s">
+      <c r="A209" s="5" t="str">
+        <f t="array" ref="A209">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A208)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B209" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B209" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C209" s="5" t="str">
         <f t="array" ref="C209">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A208)-1, 23)+1)</f>
@@ -40331,11 +40539,12 @@
       <c r="Z209" s="8"/>
     </row>
     <row r="210">
-      <c r="A210" s="11" t="s">
+      <c r="A210" s="5" t="str">
+        <f t="array" ref="A210">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A209)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B210" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B210" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C210" s="5" t="str">
         <f t="array" ref="C210">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A209)-1, 23)+1)</f>
@@ -40375,11 +40584,12 @@
       <c r="Z210" s="8"/>
     </row>
     <row r="211">
-      <c r="A211" s="11" t="s">
+      <c r="A211" s="5" t="str">
+        <f t="array" ref="A211">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A210)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B211" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B211" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C211" s="5" t="str">
         <f t="array" ref="C211">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A210)-1, 23)+1)</f>
@@ -40413,11 +40623,12 @@
       <c r="Z211" s="8"/>
     </row>
     <row r="212">
-      <c r="A212" s="11" t="s">
+      <c r="A212" s="5" t="str">
+        <f t="array" ref="A212">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A211)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B212" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B212" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C212" s="5" t="str">
         <f t="array" ref="C212">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A211)-1, 23)+1)</f>
@@ -40451,11 +40662,12 @@
       <c r="Z212" s="8"/>
     </row>
     <row r="213">
-      <c r="A213" s="11" t="s">
+      <c r="A213" s="5" t="str">
+        <f t="array" ref="A213">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A212)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B213" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B213" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C213" s="5" t="str">
         <f t="array" ref="C213">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A212)-1, 23)+1)</f>
@@ -40489,11 +40701,12 @@
       <c r="Z213" s="8"/>
     </row>
     <row r="214">
-      <c r="A214" s="11" t="s">
+      <c r="A214" s="5" t="str">
+        <f t="array" ref="A214">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A213)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B214" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B214" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C214" s="5" t="str">
         <f t="array" ref="C214">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A213)-1, 23)+1)</f>
@@ -40527,11 +40740,12 @@
       <c r="Z214" s="8"/>
     </row>
     <row r="215">
-      <c r="A215" s="11" t="s">
+      <c r="A215" s="5" t="str">
+        <f t="array" ref="A215">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A214)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B215" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B215" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C215" s="5" t="str">
         <f t="array" ref="C215">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A214)-1, 23)+1)</f>
@@ -40565,11 +40779,12 @@
       <c r="Z215" s="8"/>
     </row>
     <row r="216">
-      <c r="A216" s="11" t="s">
+      <c r="A216" s="5" t="str">
+        <f t="array" ref="A216">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A215)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B216" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B216" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C216" s="5" t="str">
         <f t="array" ref="C216">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A215)-1, 23)+1)</f>
@@ -40603,11 +40818,12 @@
       <c r="Z216" s="8"/>
     </row>
     <row r="217">
-      <c r="A217" s="11" t="s">
+      <c r="A217" s="5" t="str">
+        <f t="array" ref="A217">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A216)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B217" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B217" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C217" s="5" t="str">
         <f t="array" ref="C217">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A216)-1, 23)+1)</f>
@@ -40642,11 +40858,12 @@
       <c r="Z217" s="8"/>
     </row>
     <row r="218">
-      <c r="A218" s="11" t="s">
+      <c r="A218" s="5" t="str">
+        <f t="array" ref="A218">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A217)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B218" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B218" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C218" s="5" t="str">
         <f t="array" ref="C218">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A217)-1, 23)+1)</f>
@@ -40680,11 +40897,12 @@
       <c r="Z218" s="8"/>
     </row>
     <row r="219">
-      <c r="A219" s="11" t="s">
+      <c r="A219" s="5" t="str">
+        <f t="array" ref="A219">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A218)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B219" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B219" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C219" s="5" t="str">
         <f t="array" ref="C219">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A218)-1, 23)+1)</f>
@@ -40718,11 +40936,12 @@
       <c r="Z219" s="8"/>
     </row>
     <row r="220">
-      <c r="A220" s="11" t="s">
+      <c r="A220" s="5" t="str">
+        <f t="array" ref="A220">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A219)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B220" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B220" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C220" s="5" t="str">
         <f t="array" ref="C220">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A219)-1, 23)+1)</f>
@@ -40756,11 +40975,12 @@
       <c r="Z220" s="8"/>
     </row>
     <row r="221">
-      <c r="A221" s="11" t="s">
+      <c r="A221" s="5" t="str">
+        <f t="array" ref="A221">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A220)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B221" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B221" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C221" s="5" t="str">
         <f t="array" ref="C221">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A220)-1, 23)+1)</f>
@@ -40794,11 +41014,12 @@
       <c r="Z221" s="8"/>
     </row>
     <row r="222">
-      <c r="A222" s="11" t="s">
+      <c r="A222" s="5" t="str">
+        <f t="array" ref="A222">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A221)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B222" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B222" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C222" s="5" t="str">
         <f t="array" ref="C222">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A221)-1, 23)+1)</f>
@@ -40832,11 +41053,12 @@
       <c r="Z222" s="8"/>
     </row>
     <row r="223">
-      <c r="A223" s="11" t="s">
+      <c r="A223" s="5" t="str">
+        <f t="array" ref="A223">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A222)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B223" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B223" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C223" s="5" t="str">
         <f t="array" ref="C223">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A222)-1, 23)+1)</f>
@@ -40870,11 +41092,12 @@
       <c r="Z223" s="8"/>
     </row>
     <row r="224">
-      <c r="A224" s="11" t="s">
+      <c r="A224" s="5" t="str">
+        <f t="array" ref="A224">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A223)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B224" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B224" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C224" s="5" t="str">
         <f t="array" ref="C224">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A223)-1, 23)+1)</f>
@@ -40908,11 +41131,12 @@
       <c r="Z224" s="8"/>
     </row>
     <row r="225">
-      <c r="A225" s="11" t="s">
+      <c r="A225" s="5" t="str">
+        <f t="array" ref="A225">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A224)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B225" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B225" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C225" s="5" t="str">
         <f t="array" ref="C225">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A224)-1, 23)+1)</f>
@@ -40946,11 +41170,12 @@
       <c r="Z225" s="8"/>
     </row>
     <row r="226">
-      <c r="A226" s="11" t="s">
+      <c r="A226" s="5" t="str">
+        <f t="array" ref="A226">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A225)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B226" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B226" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C226" s="5" t="str">
         <f t="array" ref="C226">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A225)-1, 23)+1)</f>
@@ -40984,11 +41209,12 @@
       <c r="Z226" s="8"/>
     </row>
     <row r="227">
-      <c r="A227" s="11" t="s">
+      <c r="A227" s="5" t="str">
+        <f t="array" ref="A227">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A226)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B227" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B227" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C227" s="5" t="str">
         <f t="array" ref="C227">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A226)-1, 23)+1)</f>
@@ -41023,11 +41249,12 @@
       <c r="Z227" s="8"/>
     </row>
     <row r="228">
-      <c r="A228" s="11" t="s">
+      <c r="A228" s="5" t="str">
+        <f t="array" ref="A228">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A227)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B228" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B228" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C228" s="5" t="str">
         <f t="array" ref="C228">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A227)-1, 23)+1)</f>
@@ -41061,11 +41288,12 @@
       <c r="Z228" s="8"/>
     </row>
     <row r="229">
-      <c r="A229" s="11" t="s">
+      <c r="A229" s="5" t="str">
+        <f t="array" ref="A229">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A228)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B229" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B229" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C229" s="5" t="str">
         <f t="array" ref="C229">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A228)-1, 23)+1)</f>
@@ -41099,11 +41327,12 @@
       <c r="Z229" s="8"/>
     </row>
     <row r="230">
-      <c r="A230" s="11" t="s">
+      <c r="A230" s="5" t="str">
+        <f t="array" ref="A230">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A229)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B230" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B230" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C230" s="5" t="str">
         <f t="array" ref="C230">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A229)-1, 23)+1)</f>
@@ -41137,11 +41366,12 @@
       <c r="Z230" s="8"/>
     </row>
     <row r="231">
-      <c r="A231" s="11" t="s">
+      <c r="A231" s="5" t="str">
+        <f t="array" ref="A231">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A230)-1)/23)+1)</f>
+        <v>F10</v>
+      </c>
+      <c r="B231" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B231" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="C231" s="5" t="str">
         <f t="array" ref="C231">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A230)-1, 23)+1)</f>
@@ -41175,8 +41405,9 @@
       <c r="Z231" s="8"/>
     </row>
     <row r="232">
-      <c r="A232" s="11" t="s">
-        <v>30</v>
+      <c r="A232" s="5" t="str">
+        <f t="array" ref="A232">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A231)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B232" s="8"/>
       <c r="C232" s="5" t="str">
@@ -41208,8 +41439,9 @@
       <c r="Z232" s="8"/>
     </row>
     <row r="233">
-      <c r="A233" s="11" t="s">
-        <v>30</v>
+      <c r="A233" s="5" t="str">
+        <f t="array" ref="A233">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A232)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B233" s="8"/>
       <c r="C233" s="5" t="str">
@@ -41241,8 +41473,9 @@
       <c r="Z233" s="8"/>
     </row>
     <row r="234">
-      <c r="A234" s="11" t="s">
-        <v>30</v>
+      <c r="A234" s="5" t="str">
+        <f t="array" ref="A234">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A233)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B234" s="8"/>
       <c r="C234" s="5" t="str">
@@ -41274,8 +41507,9 @@
       <c r="Z234" s="8"/>
     </row>
     <row r="235">
-      <c r="A235" s="11" t="s">
-        <v>30</v>
+      <c r="A235" s="5" t="str">
+        <f t="array" ref="A235">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A234)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B235" s="8"/>
       <c r="C235" s="5" t="str">
@@ -41307,8 +41541,9 @@
       <c r="Z235" s="8"/>
     </row>
     <row r="236">
-      <c r="A236" s="11" t="s">
-        <v>30</v>
+      <c r="A236" s="5" t="str">
+        <f t="array" ref="A236">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A235)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B236" s="8"/>
       <c r="C236" s="5" t="str">
@@ -41340,8 +41575,9 @@
       <c r="Z236" s="8"/>
     </row>
     <row r="237">
-      <c r="A237" s="11" t="s">
-        <v>30</v>
+      <c r="A237" s="5" t="str">
+        <f t="array" ref="A237">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A236)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="5" t="str">
@@ -41373,8 +41609,9 @@
       <c r="Z237" s="8"/>
     </row>
     <row r="238">
-      <c r="A238" s="11" t="s">
-        <v>30</v>
+      <c r="A238" s="5" t="str">
+        <f t="array" ref="A238">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A237)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="5" t="str">
@@ -41406,8 +41643,9 @@
       <c r="Z238" s="8"/>
     </row>
     <row r="239">
-      <c r="A239" s="11" t="s">
-        <v>30</v>
+      <c r="A239" s="5" t="str">
+        <f t="array" ref="A239">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A238)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="5" t="str">
@@ -41439,8 +41677,9 @@
       <c r="Z239" s="8"/>
     </row>
     <row r="240">
-      <c r="A240" s="11" t="s">
-        <v>30</v>
+      <c r="A240" s="5" t="str">
+        <f t="array" ref="A240">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A239)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="5" t="str">
@@ -41473,8 +41712,9 @@
       <c r="Z240" s="8"/>
     </row>
     <row r="241">
-      <c r="A241" s="11" t="s">
-        <v>30</v>
+      <c r="A241" s="5" t="str">
+        <f t="array" ref="A241">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A240)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="5" t="str">
@@ -41506,8 +41746,9 @@
       <c r="Z241" s="8"/>
     </row>
     <row r="242">
-      <c r="A242" s="11" t="s">
-        <v>30</v>
+      <c r="A242" s="5" t="str">
+        <f t="array" ref="A242">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A241)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="5" t="str">
@@ -41539,8 +41780,9 @@
       <c r="Z242" s="8"/>
     </row>
     <row r="243">
-      <c r="A243" s="11" t="s">
-        <v>30</v>
+      <c r="A243" s="5" t="str">
+        <f t="array" ref="A243">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A242)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="5" t="str">
@@ -41572,8 +41814,9 @@
       <c r="Z243" s="8"/>
     </row>
     <row r="244">
-      <c r="A244" s="11" t="s">
-        <v>30</v>
+      <c r="A244" s="5" t="str">
+        <f t="array" ref="A244">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A243)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="5" t="str">
@@ -41605,8 +41848,9 @@
       <c r="Z244" s="8"/>
     </row>
     <row r="245">
-      <c r="A245" s="11" t="s">
-        <v>30</v>
+      <c r="A245" s="5" t="str">
+        <f t="array" ref="A245">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A244)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="5" t="str">
@@ -41638,8 +41882,9 @@
       <c r="Z245" s="8"/>
     </row>
     <row r="246">
-      <c r="A246" s="11" t="s">
-        <v>30</v>
+      <c r="A246" s="5" t="str">
+        <f t="array" ref="A246">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A245)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="5" t="str">
@@ -41671,8 +41916,9 @@
       <c r="Z246" s="8"/>
     </row>
     <row r="247">
-      <c r="A247" s="11" t="s">
-        <v>30</v>
+      <c r="A247" s="5" t="str">
+        <f t="array" ref="A247">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A246)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="5" t="str">
@@ -41704,8 +41950,9 @@
       <c r="Z247" s="8"/>
     </row>
     <row r="248">
-      <c r="A248" s="11" t="s">
-        <v>30</v>
+      <c r="A248" s="5" t="str">
+        <f t="array" ref="A248">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A247)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="5" t="str">
@@ -41737,8 +41984,9 @@
       <c r="Z248" s="8"/>
     </row>
     <row r="249">
-      <c r="A249" s="11" t="s">
-        <v>30</v>
+      <c r="A249" s="5" t="str">
+        <f t="array" ref="A249">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A248)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="5" t="str">
@@ -41770,8 +42018,9 @@
       <c r="Z249" s="8"/>
     </row>
     <row r="250">
-      <c r="A250" s="11" t="s">
-        <v>30</v>
+      <c r="A250" s="5" t="str">
+        <f t="array" ref="A250">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A249)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="5" t="str">
@@ -41804,8 +42053,9 @@
       <c r="Z250" s="8"/>
     </row>
     <row r="251">
-      <c r="A251" s="11" t="s">
-        <v>30</v>
+      <c r="A251" s="5" t="str">
+        <f t="array" ref="A251">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A250)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="5" t="str">
@@ -41837,8 +42087,9 @@
       <c r="Z251" s="8"/>
     </row>
     <row r="252">
-      <c r="A252" s="11" t="s">
-        <v>30</v>
+      <c r="A252" s="5" t="str">
+        <f t="array" ref="A252">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A251)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="5" t="str">
@@ -41870,8 +42121,9 @@
       <c r="Z252" s="8"/>
     </row>
     <row r="253">
-      <c r="A253" s="11" t="s">
-        <v>30</v>
+      <c r="A253" s="5" t="str">
+        <f t="array" ref="A253">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A252)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="5" t="str">
@@ -41903,8 +42155,9 @@
       <c r="Z253" s="8"/>
     </row>
     <row r="254">
-      <c r="A254" s="11" t="s">
-        <v>30</v>
+      <c r="A254" s="5" t="str">
+        <f t="array" ref="A254">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A253)-1)/23)+1)</f>
+        <v>F11</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="5" t="str">
@@ -41936,7 +42189,10 @@
       <c r="Z254" s="8"/>
     </row>
     <row r="255">
-      <c r="A255" s="8"/>
+      <c r="A255" s="5" t="str">
+        <f t="array" ref="A255">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A254)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
       <c r="D255" s="8"/>
@@ -41964,7 +42220,10 @@
       <c r="Z255" s="8"/>
     </row>
     <row r="256">
-      <c r="A256" s="8"/>
+      <c r="A256" s="5" t="str">
+        <f t="array" ref="A256">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A255)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
       <c r="D256" s="8"/>
@@ -41992,7 +42251,10 @@
       <c r="Z256" s="8"/>
     </row>
     <row r="257">
-      <c r="A257" s="8"/>
+      <c r="A257" s="5" t="str">
+        <f t="array" ref="A257">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A256)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
       <c r="D257" s="8"/>
@@ -42020,7 +42282,10 @@
       <c r="Z257" s="8"/>
     </row>
     <row r="258">
-      <c r="A258" s="8"/>
+      <c r="A258" s="5" t="str">
+        <f t="array" ref="A258">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A257)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
       <c r="D258" s="8"/>
@@ -42048,7 +42313,10 @@
       <c r="Z258" s="8"/>
     </row>
     <row r="259">
-      <c r="A259" s="8"/>
+      <c r="A259" s="5" t="str">
+        <f t="array" ref="A259">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A258)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B259" s="8"/>
       <c r="C259" s="8"/>
       <c r="D259" s="8"/>
@@ -42076,7 +42344,10 @@
       <c r="Z259" s="8"/>
     </row>
     <row r="260">
-      <c r="A260" s="8"/>
+      <c r="A260" s="5" t="str">
+        <f t="array" ref="A260">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A259)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B260" s="8"/>
       <c r="C260" s="8"/>
       <c r="D260" s="8"/>
@@ -42104,7 +42375,10 @@
       <c r="Z260" s="8"/>
     </row>
     <row r="261">
-      <c r="A261" s="8"/>
+      <c r="A261" s="5" t="str">
+        <f t="array" ref="A261">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A260)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B261" s="8"/>
       <c r="C261" s="8"/>
       <c r="D261" s="8"/>
@@ -42132,7 +42406,10 @@
       <c r="Z261" s="8"/>
     </row>
     <row r="262">
-      <c r="A262" s="8"/>
+      <c r="A262" s="5" t="str">
+        <f t="array" ref="A262">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A261)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B262" s="8"/>
       <c r="C262" s="8"/>
       <c r="D262" s="8"/>
@@ -42160,7 +42437,10 @@
       <c r="Z262" s="8"/>
     </row>
     <row r="263">
-      <c r="A263" s="8"/>
+      <c r="A263" s="5" t="str">
+        <f t="array" ref="A263">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A262)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B263" s="8"/>
       <c r="C263" s="8"/>
       <c r="D263" s="8"/>
@@ -42188,7 +42468,10 @@
       <c r="Z263" s="8"/>
     </row>
     <row r="264">
-      <c r="A264" s="8"/>
+      <c r="A264" s="5" t="str">
+        <f t="array" ref="A264">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A263)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B264" s="8"/>
       <c r="C264" s="8"/>
       <c r="D264" s="8"/>
@@ -42216,7 +42499,10 @@
       <c r="Z264" s="8"/>
     </row>
     <row r="265">
-      <c r="A265" s="8"/>
+      <c r="A265" s="5" t="str">
+        <f t="array" ref="A265">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A264)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B265" s="8"/>
       <c r="C265" s="8"/>
       <c r="D265" s="8"/>
@@ -42244,7 +42530,10 @@
       <c r="Z265" s="8"/>
     </row>
     <row r="266">
-      <c r="A266" s="8"/>
+      <c r="A266" s="5" t="str">
+        <f t="array" ref="A266">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A265)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B266" s="8"/>
       <c r="C266" s="8"/>
       <c r="D266" s="8"/>
@@ -42272,7 +42561,10 @@
       <c r="Z266" s="8"/>
     </row>
     <row r="267">
-      <c r="A267" s="8"/>
+      <c r="A267" s="5" t="str">
+        <f t="array" ref="A267">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A266)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B267" s="8"/>
       <c r="C267" s="8"/>
       <c r="D267" s="8"/>
@@ -42300,7 +42592,10 @@
       <c r="Z267" s="8"/>
     </row>
     <row r="268">
-      <c r="A268" s="8"/>
+      <c r="A268" s="5" t="str">
+        <f t="array" ref="A268">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A267)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B268" s="8"/>
       <c r="C268" s="8"/>
       <c r="D268" s="8"/>
@@ -42328,7 +42623,10 @@
       <c r="Z268" s="8"/>
     </row>
     <row r="269">
-      <c r="A269" s="8"/>
+      <c r="A269" s="5" t="str">
+        <f t="array" ref="A269">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A268)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B269" s="8"/>
       <c r="C269" s="8"/>
       <c r="D269" s="8"/>
@@ -42356,7 +42654,10 @@
       <c r="Z269" s="8"/>
     </row>
     <row r="270">
-      <c r="A270" s="8"/>
+      <c r="A270" s="5" t="str">
+        <f t="array" ref="A270">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A269)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B270" s="8"/>
       <c r="C270" s="8"/>
       <c r="D270" s="8"/>
@@ -42384,7 +42685,10 @@
       <c r="Z270" s="8"/>
     </row>
     <row r="271">
-      <c r="A271" s="8"/>
+      <c r="A271" s="5" t="str">
+        <f t="array" ref="A271">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A270)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B271" s="8"/>
       <c r="C271" s="8"/>
       <c r="D271" s="8"/>
@@ -42412,7 +42716,10 @@
       <c r="Z271" s="8"/>
     </row>
     <row r="272">
-      <c r="A272" s="8"/>
+      <c r="A272" s="5" t="str">
+        <f t="array" ref="A272">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A271)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B272" s="8"/>
       <c r="C272" s="8"/>
       <c r="D272" s="8"/>
@@ -42440,7 +42747,10 @@
       <c r="Z272" s="8"/>
     </row>
     <row r="273">
-      <c r="A273" s="8"/>
+      <c r="A273" s="5" t="str">
+        <f t="array" ref="A273">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A272)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
       <c r="D273" s="8"/>
@@ -42468,7 +42778,10 @@
       <c r="Z273" s="8"/>
     </row>
     <row r="274">
-      <c r="A274" s="8"/>
+      <c r="A274" s="5" t="str">
+        <f t="array" ref="A274">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A273)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B274" s="8"/>
       <c r="C274" s="8"/>
       <c r="D274" s="8"/>
@@ -42496,7 +42809,10 @@
       <c r="Z274" s="8"/>
     </row>
     <row r="275">
-      <c r="A275" s="8"/>
+      <c r="A275" s="5" t="str">
+        <f t="array" ref="A275">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A274)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
       <c r="D275" s="8"/>
@@ -42524,7 +42840,10 @@
       <c r="Z275" s="8"/>
     </row>
     <row r="276">
-      <c r="A276" s="8"/>
+      <c r="A276" s="5" t="str">
+        <f t="array" ref="A276">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A275)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
       <c r="D276" s="8"/>
@@ -42552,7 +42871,10 @@
       <c r="Z276" s="8"/>
     </row>
     <row r="277">
-      <c r="A277" s="8"/>
+      <c r="A277" s="5" t="str">
+        <f t="array" ref="A277">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A276)-1)/23)+1)</f>
+        <v>F12</v>
+      </c>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
       <c r="D277" s="8"/>
@@ -42580,7 +42902,10 @@
       <c r="Z277" s="8"/>
     </row>
     <row r="278">
-      <c r="A278" s="8"/>
+      <c r="A278" s="5" t="str">
+        <f t="array" ref="A278">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A277)-1)/23)+1)</f>
+        <v>F13</v>
+      </c>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
       <c r="D278" s="8"/>
@@ -42608,7 +42933,10 @@
       <c r="Z278" s="8"/>
     </row>
     <row r="279">
-      <c r="A279" s="8"/>
+      <c r="A279" s="5" t="str">
+        <f t="array" ref="A279">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A278)-1)/23)+1)</f>
+        <v>F13</v>
+      </c>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
       <c r="D279" s="8"/>
@@ -42636,7 +42964,7 @@
       <c r="Z279" s="8"/>
     </row>
     <row r="280">
-      <c r="A280" s="8"/>
+      <c r="A280" s="5"/>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
       <c r="D280" s="8"/>
@@ -42664,7 +42992,7 @@
       <c r="Z280" s="8"/>
     </row>
     <row r="281">
-      <c r="A281" s="8"/>
+      <c r="A281" s="5"/>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
       <c r="D281" s="8"/>
@@ -42692,7 +43020,7 @@
       <c r="Z281" s="8"/>
     </row>
     <row r="282">
-      <c r="A282" s="8"/>
+      <c r="A282" s="5"/>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
       <c r="D282" s="8"/>

--- a/02-data/03-final-RA.xlsx
+++ b/02-data/03-final-RA.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="572">
   <si>
     <t>framework_id</t>
   </si>
@@ -1388,6 +1388,9 @@
     <t xml:space="preserve">visualization by TensorBoard. </t>
   </si>
   <si>
+    <t>TensorBoard</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <color rgb="FF1155CC"/>
@@ -2717,9 +2720,6 @@
 def plot_results/ plot_curves</t>
   </si>
   <si>
-    <t>TensorBoard</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://github.com/DLR-RM/rl-baselines3-zoo/blob/master/rl_zoo3/train.py  </t>
   </si>
   <si>
@@ -2957,6 +2957,39 @@
   </si>
   <si>
     <t>manage RLlib experiments through an instance of the Algorithm class, share class with Framework Orchestrator, mix responsibilities</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/ray-project/ray/blob/master/python/ray/tune/tuner.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>class Tuner:
+    """Tuner is the recommended way of launching hyperparameter tuning jobs with Ray Tune.
+tune.Tuner(
+    config.algo_class,
+    param_space=config,
+    # Specify a stopping criterion. Note that the criterion has to match one of the
+    # pretty printed result metrics from the results returned previously by
+    # ``.train()``. Also note that -1100 is not a good episode return for
+    # Pendulum-v1, we are using it here to shorten the experiment time.
+    run_config=tune.RunConfig(
+        stop={"env_runners/episode_return_mean": -1100.0},
+    ),
+)
+# Run the Tuner and capture the results.
+results = tuner.fit()</t>
+  </si>
+  <si>
+    <t>Ray Tune</t>
   </si>
   <si>
     <r>
@@ -3622,9 +3655,6 @@
 results = tuner.fit()</t>
   </si>
   <si>
-    <t>Ray Tune</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <color rgb="FF1155CC"/>
@@ -3852,6 +3882,1378 @@
   </si>
   <si>
     <t>Command-line reporter</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/experiment/experiment.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">benchmarl/experiment/experiment.py
+class Experiment(CallbackNotifier):
+    """
+    Main experiment class in BenchMARL.
+An experiment is a training run in which an algorithm, a task, and a model are fixed. </t>
+  </si>
+  <si>
+    <t>train, evaluate, checkpoint</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/benchmark/benchmark.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">class Benchmark:  
+"""A benchmark.
+Benchmarks are collections of experiments to compare.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/experiment/experiment.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>class Experiment(CallbackNotifier):
+def run(self):
+        """Run the experiment until completion."""
+        try:
+            seed_everything(self.seed)
+            torch.cuda.empty_cache()
+            self._collection_loop()
+        except KeyboardInterrupt as interrupt:
+            print("\n\nExperiment was closed gracefully\n\n")
+            self.close()
+            raise interrupt
+        except Exception as err:
+            print("\n\nExperiment failed and is closing gracefully\n\n")
+            self.close()
+            raise err</t>
+  </si>
+  <si>
+    <t>execute run() -&gt; get into the train loop, with orchestrator, agent, env</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/experiment/experiment.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>benchmarl/experiment/experiment.py
+class Experiment(CallbackNotifier):
+def _collection_loop(self):
+ # Training/collection iterations
+# Logging</t>
+  </si>
+  <si>
+    <t>collect data, update policy</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/run.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> ;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/hydra_config.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>if _has_hydra:
+    from hydra import compose, initialize, initialize_config_dir
+    from omegaconf import DictConfig, OmegaConf</t>
+  </si>
+  <si>
+    <t>Hydra for flexible and modular configuration</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/algorithms/iql.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>experiment_config.share_policy_params = True # Policy parameter sharing on
+BenchMARL will automatically group agents based on the VMAS name 
+This allows to stack their data because they are homogeneous.
+Agents from different groups will be kept separate and it is even possible to use different models 
+and algorithms for different groups. 
+It is possible to use different algorithms and models for different agent groups.</t>
+  </si>
+  <si>
+    <t>In algorithms/ folder for each algorithm, for example:
+((all cars togherther, all holonomic together, all differential drive together).
+implementation in algorithm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/algorithms/common.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">class Algorithm(ABC):
+    """
+    Abstract class for an algorithm.
+Algorithms. 
+Algorithms are an ensemble of components (e.g., losss, replay buffer) 
+which determine the training strategy. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/tree/main/benchmarl/models</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> ;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/models/common.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Models are neural networks used to process data. 
+They can be used as actors (policies) or, when requested, as critics. 
+We provide a set of base models (layers) and a SequenceModel to concatenate different layers. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/environments/common.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>benchmarl/environments/common.py
+torch.data.ReplayBuffer
+A generic, composable replay buffer class.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/algorithms/common.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>def get_policy_for_loss(self, group: str) -&gt; TensorDictModule:
+        """
+        Get the non-explorative policy for a specific group loss.
+        This function calls the abstract :class:`~benchmarl.algorithms.Algorithm._get_policy_for_loss()` which needs to be implemented.
+        The function will cache the output at the first call and return the cached values in future calls.
+        Args:
+            group (str): agent group of the policy
+        Returns: TensorDictModule representing the policy
+        """
+        if group not in self._policies_for_loss.keys():
+            action_space = self.action_spec[group, "action"]
+            continuous = not isinstance(action_space, (Categorical, OneHot))
+            self._policies_for_loss.update(
+                {
+                    group: self._get_policy_for_loss(
+                        group=group,
+                        continuous=continuous,
+                        model_config=self.model_config,
+                    )
+                }
+            )
+        return self._policies_for_loss[group]</t>
+  </si>
+  <si>
+    <t>inside class Algorithm(ABC), not a seperate module</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/examples/checkpointing/reload_experiment.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> ;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/examples/checkpointing/resume_experiment.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>examples/checkpointing/reload_experiment.py
+  # Save the experiment in the current folder
+    experiment_config.save_folder = Path(os.path.dirname(os.path.realpath(__file__)))
+    # Checkpoint at every iteration
+-----
+examples/checkpointing/resume_experiment.py
+reload_experiment_from_file
+ # Now we tell it where to resume from
+    restored_experiment = reload_experiment_from_file(
+        (
+            experiment.folder_name
+            / "checkpoints"
+            / f"checkpoint_{experiment_config.checkpoint_interval}.pt"
+        )
+    )  # Restore from first checkpoint</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/experiment/logger.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>benchmarl/experiment/logger.py
+class Logger
+ def log_evaluation(
+logger.log_video("eval_video", vid, step=step)
+logger.log_video("eval/video", vid, fps=20, commit=False)</t>
+  </si>
+  <si>
+    <t>inside logger, not a seperate module, only the function</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/experiment/logger.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>benchmarl/experiment/logger.py
+class Logger
+from torchrl.record import TensorboardLogger
+from torchrl.record.loggers import get_logger
+from torchrl.record.loggers.wandb import WandbLogger</t>
+  </si>
+  <si>
+    <t>BenchMARL is compatible with the TorchRL loggers.</t>
+  </si>
+  <si>
+    <t>TorchRL loggers</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/facebookresearch/BenchMARL/blob/main/benchmarl/eval_results.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/marl-eval/tree/main/marl_eval/plotting_tools</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>benchmarl/eval_results.py
+import collections
+import importlib
+class Plotting:
+Class containing static utilities for plotting in ``marl-eval``.
+from benchmarl.eval_results import load_and_merge_json_dicts, Plotting
+ # Plotting
+    Plotting.performance_profile_figure(
+        environment_comparison_matrix=environment_comparison_matrix
+    )
+    Plotting.aggregate_scores(
+        environment_comparison_matrix=environment_comparison_matrix
+    )
+    Plotting.environemnt_sample_efficiency_curves(
+        sample_effeciency_matrix=sample_efficiency_matrix
+    )
+    Plotting.task_sample_efficiency_curves(
+        processed_data=processed_data, env="vmas", task="navigation"
+    )
+    Plotting.probability_of_improvement(
+        environment_comparison_matrix,
+        algorithms_to_compare=[["qmix", "mappo"]],
+    )
+    plt.show()
+-----
+marl_eval/plotting_tools
+from marl_eval.plotting_tools.plotting import (
+        aggregate_scores,
+        performance_profiles,
+        plot_single_task,
+        probability_of_improvement,
+        sample_efficiency_curves,
+    )
+    from marl_eval.utils.data_processing_utils import (
+        create_matrices_for_rliable,
+        data_process_pipeline,
+    )
+    from matplotlib import pyplot as plt</t>
+  </si>
+  <si>
+    <t>Plotting</t>
+  </si>
+  <si>
+    <t>marl_eval/plotting_tools</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/tree/develop/mava/systems</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/blob/develop/mava/systems/ppo/anakin/ff_ippo.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>def run_experiment(_config: DictConfig) -&gt; float:
+    """Runs experiment."""
+setup environment, logging, checkpoint, 
+learn, actor_network, learner_state = learner_setup(
+        env, (key, actor_net_key, critic_net_key), config
+    )
+learn, evaluate, output</t>
+  </si>
+  <si>
+    <t>mava/systems
+(each algorithm one file)
+For example the link here.
+mix responsibilities with the Framework Orchestrator.
+The Experiment Manager sets up the Utilities components
+(e.g., Checkpoint Manager)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/tree/develop/mava/systems</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/blob/develop/mava/systems/ppo/anakin/ff_ippo.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>mava/systems
+(each algorithm one file)
+For example the link here.
+learn, evaluate, output
+mix responsibilities with the Experiment Manager.
+the Framework Orchestrator sets up the framework components (e.g., Agent and Lifecycle Manager), and orchestrates their operation.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/blob/develop/mava/systems/gpo/anakin/rec_magpo.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>def _env_step(
+            learner_state: LearnerState, _: Any
+        ) -&gt; Tuple[LearnerState, Tuple[Transition, Metrics]]:
+            """Step the environment."""</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> inside Algorithm, for example the link here,
+step through, info change between env and agent</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/tree/develop</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> ;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/blob/develop/mava/systems/ppo/anakin/ff_ippo.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Mava makes use of Hydra for config management. In order to see our default system configs please see the mava/configs/ directory. A benefit of Hydra is that configs can either be set in config yaml files or overwritten from the terminal on the fly. 
+----
+from omegaconf import DictConfig, OmegaConf
+import hydra
+Hydra's configuration object is an instance of OmegaConf's DictConfig.
+config: DictConfig = OmegaConf.create(config)
+def hydra_entry_point(cfg: DictConfig) -&gt; float:
+    """Experiment entry point."""
+    # Allow dynamic attributes.
+    OmegaConf.set_struct(cfg, False)
+    # Run experiment.
+    eval_performance = run_experiment(cfg)
+    print(f"{Fore.CYAN}{Style.BRIGHT}IPPO experiment completed{Style.RESET_ALL}")
+    return eval_performance
+if __name__ == "__main__":
+    hydra_entry_point()
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/blob/develop/mava/systems/sac/anakin/ff_isac.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t># Number of env steps before evaluating/logging.
+    steps_per_rollout = int(cfg.system.total_timesteps // cfg.arch.num_evaluation)
+    # Multiplier for a single env/learn step in an anakin system
+    anakin_steps = cfg.arch.n_devices * cfg.system.update_batch_size
+    # Number of env steps in one anakin style update.
+    anakin_act_steps = anakin_steps * cfg.arch.num_envs * cfg.system.rollout_length
+    # Number of steps to do in the scanned update method (how many anakin steps).
+    cfg.system.scan_steps = int(steps_per_rollout / anakin_act_steps)
+# Distribute params and opt states across all devices
+    params = replicate(params)
+    opt_states = replicate(opt_states)</t>
+  </si>
+  <si>
+    <t>support distribution, but not a complete module.
+Anakin architecture (Hessel et al., 2021) for scalable distributed system training on hardware
+accelerators
+Mava supports both Podracer architectures for scaling RL systems. The first of these is Anakin, which can be used when environments are written in JAX. This enables end-to-end JIT compilation of the full MARL training loop for fast experiment run times on hardware accelerators. The second is Sebulba, which can be used when environments are not written in JAX. Sebulba is particularly useful when running RL experiments where a hardware accelerator can interact with many CPU cores at a time.</t>
+  </si>
+  <si>
+    <t>https://github.com/instadeepai/Mava/blob/develop/mava/systems/ppo/anakin/rec_mappo.py</t>
+  </si>
+  <si>
+    <t># Step environment for rollout length
+        learner_state, (traj_batch, episode_metrics) = jax.lax.scan(
+            _env_step, learner_state, length=config.system.rollout_length
+        )
+        # Calculate advantage
+        params, opt_states, key, env_state, last_timestep, last_done, updated_hstates = (
+            learner_state
+        )</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/tree/develop/mava/networks</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/blob/develop/mava/networks/base.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Actor(nn.Module)/Critic()
+from mava.networks.base import (
+    FeedForwardActor,
+    FeedForwardQNet,
+    FeedForwardValueNet,
+    RecQNetwork,
+    RecurrentActor,
+    RecurrentValueNet,
+    ScannedRNN,
+)</t>
+  </si>
+  <si>
+    <t>only the complete network module, seperate implementations, implement nn,Module, but all the function approcximator logics are merged into the each single algorithm implementaion. not modular.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/instadeepai/Mava/blob/develop/mava/systems/sac/anakin/ff_isac.p </t>
+  </si>
+  <si>
+    <t>import flashbax as fbx
+from colorama import Fore, Style
+from flashbax.buffers.flat_buffer import TrajectoryBuffer
+ # Create replay buffer
+    init_transition = Transition(
+        obs=obs,
+        action=acts,
+        reward=jnp.zeros((n_agents,), dtype=float),
+        done=jnp.zeros((n_agents,), dtype=bool),
+        next_obs=obs,
+    )
+    rb = fbx.make_item_buffer(
+        max_length=int(cfg.system.buffer_size),
+        min_length=int(cfg.system.explore_steps),
+        sample_batch_size=int(cfg.system.batch_size),
+        add_batches=True,
+    )
+    buffer_state = replicate(rb.init(init_transition))</t>
+  </si>
+  <si>
+    <t>FlashBax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/instadeepai/Mava/blob/develop/mava/systems/sac/anakin/ff_isac.py  </t>
+  </si>
+  <si>
+    <t>data = rb.sample(buffer_state, buff_key).experience
+params, opt_states, q_loss_info = update_q(params, opt_states, data, q_key)
+# Sample and learn
+        learn_state = (buffer_state, params, opt_states, t, learn_key)
+        (buffer_state, params, opt_states, _, _), losses = scanned_train(learn_state)
+        t += cfg.arch.num_envs * cfg.system.rollout_length
+        return (
+            LearnerState(next_obs, env_state, buffer_state, params, opt_states, t, key),
+            (metrics, losses),
+        )
+learner_setup
+def get_learner_fn(
+    env: jumanji.Environment,
+    apply_fns: Tuple[ActorApply, CriticApply],
+    update_fns: Tuple[optax.TransformUpdateFn, optax.TransformUpdateFn],
+    config: DictConfig,
+) -&gt; LearnerFn[LearnerState]:
+    """Get the learner function."""
+    # Unpack apply and update functions.
+    actor_apply_fn, critic_apply_fn = apply_fns
+    actor_update_fn, critic_update_fn = update_fns
+    def _update_step(learner_state: LearnerState, _: Any) -&gt; Tuple[LearnerState, Tuple]:
+        """A single update of the network.
+ def learner_fn(learner_state: LearnerState) -&gt; ExperimentOutput[LearnerState]:
+        """Learner function.</t>
+  </si>
+  <si>
+    <t>all the learner logics are merged into the each single algorithm implementaion. 
+not modular.
+(learner_func here, but no learner)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/blob/develop/mava/utils/checkpointing.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>mava/utils/checkpointing.py
+class Checkpointer:
+Model checkpointer for saving and restoring the `learner_state`.
+import orbax.checkpoint</t>
+  </si>
+  <si>
+    <t>Orbax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/instadeepai/Mava/blob/develop/mava/utils/logger.py </t>
+  </si>
+  <si>
+    <t>mava/utils/logger.py
+class MavaLogger:
+    def __init__(
+        self,
+        config: DictConfig,
+        custom_metrics_fn: Callable[[Metrics], Metrics] = winrate_custom_metric,
+    ) -&gt; None:
+        """The main logger for Mava systems.
+class NeptuneLogger(BaseLogger):
+    def __init__(
+        self,
+        base_exp_path: PathLike,
+        unique_token: str,
+        system_name: str,
+        project: str,
+        tag: list[str],
+        group_tag: list[str],
+        detailed_logging: bool,
+        architecture_name: str,
+        upload_json_data: bool,
+        run_id: str | None = None,
+    ) -&gt; None:
+        """
+        Initialize neptune.ai logger for experiment tracking.
+class TensorboardLogger(BaseLogger):
+    def __init__(self, base_exp_path: PathLike, unique_token: str, system_name: str) -&gt; None:
+        """
+        Initialize TensorBoard logger for visualization.
+        Args:
+            base_exp_path: Base path where logs will be stored
+            unique_token: Unique identifier string for this run
+            system_name: Name of the system/algorithm being logged
+        """</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neptune, Tensorboard
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/instadeepai/Mava/blob/develop/mava/utils/logger.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>class TensorboardLogger(BaseLogger):
+    def __init__(self, base_exp_path: PathLike, unique_token: str, system_name: str) -&gt; None:
+        """
+        Initialize TensorBoard logger for visualization.</t>
+  </si>
+  <si>
+    <t>tensorboard for visualization</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/discrete_domains/run_experiment.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>dopamine/discrete_domains/run_experiment.py
+@gin.configurable
+class Runner(object):
+  """Object that handles running Dopamine experiments.
+Here we use the term 'experiment' to mean simulating interactions between the agent and the environment and reporting some statistics pertaining to these interactions.</t>
+  </si>
+  <si>
+    <t>create checkpoint, logging
+save, summarize
+mix responsibilities with the Framework Orchestrator.
+The Experiment Manager sets up the Utilities components
+(e.g., Checkpoint Manager)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/discrete_domains/run_experiment.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>create env, agent,
+initialize, run
+mix responsibilities with the Experiment Manager.
+the Framework Orchestrator sets up the framework components (e.g., Agent and Lifecycle Manager), and orchestrates their operation.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/discrete_domains/run_experiment.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/jax/agents/full_rainbow/full_rainbow_agent.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>run
+def _run_train_phase(self, statistics):
+    """Run training phase.
+def _run_eval_phase(self, statistics):
+    """Run evaluation phase.
+-----
+def _train_step(self):
+    """Runs a single training step.
+    Runs training if both:
+      (1) A minimum number of frames have been added to the replay buffer.
+      (2) `training_steps` is a multiple of `update_period`.</t>
+  </si>
+  <si>
+    <t>run call agent.train_step
+train_step: agent &lt;-&gt; env</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/discrete_domains/run_experiment.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>def load_gin_configs(gin_files, gin_bindings):
+  """Loads gin configuration files.
+  Args:
+    gin_files: list, of paths to the gin configuration files for this
+      experiment.
+    gin_bindings: list, of gin parameter bindings to override the values in the
+      config files.
+  """
+  gin.parse_config_files_and_bindings(
+      gin_files, bindings=gin_bindings, skip_unknown=False
+  )
+Gin Config, lightweight configuration framework
+The whole of Dopamine is easily configured using the gin configuration framework.</t>
+  </si>
+  <si>
+    <t>Gin</t>
+  </si>
+  <si>
+    <t>https://github.com/google/dopamine/tree/master/dopamine/jax/agents</t>
+  </si>
+  <si>
+    <t>class JaxDQNAgent(object):
+  """A JAX implementation of the DQN agent."""</t>
+  </si>
+  <si>
+    <t>for each diffeernt type algorithm they have different agent
+The agent class, in dopamine/agents.
+for example, DQNAgent</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/jax/agents/dqn/dqn_agent.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>agent.def _record_observation(self, observation):
+    """Records an observation and update state.
+def select_action(
+def step(self, reward, observation):
+    """Returns the agent's next action and update agent's state.</t>
+  </si>
+  <si>
+    <t>functions have the responsibilities of Function Approximator, but not a seperate module, they are merged into Agent.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/jax/replay_memory/replay_buffer.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>dopamine/jax/replay_memory/replay_buffer.py
+class ReplayBuffer(checkpointers.Checkpointable, Generic[ReplayElementT]):
+  """A Jax re-implementation of the Dopamine Replay Buffer.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/labs/offline_rl/jax/offline_dqn_agent.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>def step(self, reward, observation):
+    """Returns the agent's next action and update agent's state.</t>
+  </si>
+  <si>
+    <t>functions have the responsibilities of Learner, but not a seperate module, they are merged into Agent.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/discrete_domains/checkpointer.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>dopamine/discrete_domains/checkpointer.py
+"""A checkpointing mechanism for Dopamine agents.
+from absl import logging
+from dopamine.discrete_domains import atari_lib
+from dopamine.discrete_domains import checkpointer
+from dopamine.discrete_domains import iteration_statistics
+from dopamine.discrete_domains import logger
+class Checkpointer(object):
+  """Class for managing checkpoints for Dopamine agents."""</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/utils/agent_visualizer.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>class AgentVisualizer(object):
+  """Code to visualize an agent's behaviour."""
+  def __init__(
+      self,
+      record_path,
+      plotters,
+      screen_width=160,
+      screen_height=210,
+      render_rate=1,
+      file_types=('png', ''),
+      filename_format='frame_{:06d}',
+  ):
+    """Constructor for the AgentVisualizer class.
+This class generates a series of images built by a set of Plotters. These images are then saved to disk.
+It can optionally generate a video by concatenating all the images with ffmpeg.</t>
+  </si>
+  <si>
+    <t>This class generates a series of images built by a set of Plotters. These images are then saved to disk.
+It can optionally generate a video by concatenating all the images with ffmpeg.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/discrete_domains/logger.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>dopamine/discrete_domains/logger.py
+class Logger(object):
+  """Class for maintaining a dictionary of data to log."""</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/google/dopamine/blob/master/dopamine/continuous_domains/run_experiment.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>def _save_tensorboard_summaries(
+      self, iteration, num_episodes, average_reward, average_steps_per_second
+  ):
+    """Save statistics as tensorboard summaries."""
+    if self._summary_writer is None:
+      return
+    if self._sess is None:
+      with self._summary_writer.as_default():
+        tf.summary.scalar('Train/NumEpisodes', num_episodes, step=iteration)
+        tf.summary.scalar(
+            'Train/AverageReturns', average_reward, step=iteration
+        )
+        tf.summary.scalar(
+            'Train/AverageStepsPerSecond',
+            average_steps_per_second,
+            step=iteration,
+        )
+      self._summary_writer.flush()
+    else:
+      summary = tf.compat.v1.Summary(
+          value=[
+              tf.compat.v1.Summary.Value(
+                  tag='Train/NumEpisodes', simple_value=num_episodes
+              ),
+              tf.compat.v1.Summary.Value(
+                  tag='Train/AverageReturns', simple_value=average_reward
+              ),
+              tf.compat.v1.Summary.Value(
+                  tag='Train/AverageStepsPerSecond',
+                  simple_value=average_steps_per_second,
+              ),
+          ]
+      )
+      self._summary_writer.add_summary(summary, iteration)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/thu-ml/tianshou/blob/master/tianshou/highlevel/experiment.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>tianshou/highlevel/experiment.py
+The experiment module provides high-level interfaces 
+for setting up and running reinforcement learning experiments.</t>
+  </si>
+  <si>
+    <t>setup, checkpoint, run, collect result,
+persistence and the overall experiment flow</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/thu-ml/tianshou/blob/master/tianshou/trainer.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">tianshou/trainer.py
+This module contains Tianshou's trainer classes, which orchestrate the training and call upon an RL algorithm's
+specific network updating logic to perform the actual gradient updates.
+The base class already implements the fundamental epoch logic and fully implements the test step
+logic, which is common to all trainers. </t>
+  </si>
+  <si>
+    <t>controls fundamental training parameters, such as the total number of epochs we run the experiment for</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/thu-ml/tianshou/blob/master/tianshou/trainer.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>tianshou/trainer.py
+def run(
+        self, reset_collectors: bool = True, reset_collector_buffers: bool = False
+    ) -&gt; InfoStats:
+        """Runs the training process with the configuration given at construction.
+def _training_step(self) -&gt; _TrainingStepResult:
+        """Performs one training step."""</t>
+  </si>
+  <si>
+    <t>run: world.trainer.run() 
+(env &lt;-&gt; agent, function indie the framework orchestrator, not a seperate module here)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/thu-ml/tianshou/blob/master/tianshou/highlevel/config.py </t>
+  </si>
+  <si>
+    <t>tianshou/config.py
+tianshou/highlevel/config.py
+class TrainingConfig(ToStringMixin):
+    """Training configuration."""</t>
+  </si>
+  <si>
+    <t>https://github.com/thu-ml/tianshou/blob/master/tianshou/algorithm/multiagent/marl.py</t>
+  </si>
+  <si>
+    <t>tianshou/algorithm/multiagent/marl.py
+class MultiAgentPolicy(Policy):
+def forward(  # type: ignore
+        self,
+        batch: Batch,
+        state: dict | Batch | None = None,
+        **kwargs: Any,
+    ) -&gt; Batch:
+        """Dispatch batch data from obs.agent_id to every policy's forward.
+preprocess batch, update batch
+ for agent_id, policy in self.policies.items():
+            # This part of code is difficult to understand.
+            # Let's follow an example with two agents
+            # batch.obs.agent_id is [1, 2, 1, 2, 1, 2] (with batch_size == 6)
+            # each agent plays for three transitions
+            # agent_index for agent 1 is [0, 2, 4]
+            # agent_index for agent 2 is [1, 3, 5]
+            # we separate the transition of each agent according to agent_id
+            agent_index = np.nonzero(batch.obs.agent_id == agent_id)[0]</t>
+  </si>
+  <si>
+    <t>Dispatch batch data from obs.agent_id to every policy's forward.
+separate the transition of each agent according to agent_id
+policy coordination for MARL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/thu-ml/tianshou/tree/master/tianshou/algorithm  ;
+https://github.com/thu-ml/tianshou/blob/master/tianshou/algorithm/algorithm_base.py</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>class Algorithm(torch.nn.Module, Generic[TPolicy, TTrainerParams], ABC):</t>
+  </si>
+  <si>
+    <t>tianshou/algorithm (different algorithms in the folder)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/thu-ml/tianshou/blob/master/tianshou/algorithm/algorithm_base.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>class Policy(nn.Module, ABC):
+    """Represents a policy, which provides the fundamental mapping from observations to actions."""</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/thu-ml/tianshou/blob/master/tianshou/data/buffer</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> ;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/thu-ml/tianshou/blob/master/tianshou/data/buffer/buffer_base.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>class ReplayBuffer:
+    """:class:`~tianshou.data.ReplayBuffer` stores data generated from interaction between the policy and environment.
+    ReplayBuffer can be considered as a specialized form (or management) of Batch. It
+    stores all the data in a batch with circular-queue style.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/thu-ml/tianshou/blob/master/tianshou/algorithm/algorithm_base.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>class Optimizer:
+        """Wrapper for a torch optimizer that optionally performs gradient clipping."""</t>
+  </si>
+  <si>
+    <t>Optimizer has the same role as Learner</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/thu-ml/tianshou/blob/master/tianshou/highlevel/persistence.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>tianshou/highlevel/persistence.py
+def get_save_checkpoint_fn(self, world: World) -&gt; Callable[[int, int, int], str] | None:
+        if not self.enabled:
+            return None
+        def save_checkpoint_fn(epoch: int, env_step: int, gradient_step: int) -&gt; str:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://github.com/thu-ml/tianshou/blob/master/tianshou/highlevel/logger.py</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>tianshou/highlevel/logger.py
+from tianshou.utils import BaseLogger, TensorboardLogger, WandbLogger
+"""A logger that relies on tensorboard SummaryWriter by default to visualize and log statistics.</t>
+  </si>
+  <si>
+    <t>TensorboardLogger
+WandbLogger</t>
+  </si>
+  <si>
+    <t>TensorboardLogger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/thu-ml/tianshou/blob/master/tianshou/highlevel/logger.py </t>
+  </si>
+  <si>
+    <t>tensorboard SummaryWriter</t>
+  </si>
+  <si>
+    <t>Tensorboard SummaryWriter</t>
   </si>
 </sst>
 </file>
@@ -33343,7 +34745,7 @@
     <col customWidth="1" min="3" max="3" width="19.13"/>
     <col customWidth="1" min="4" max="4" width="15.88"/>
     <col customWidth="1" min="5" max="5" width="26.25"/>
-    <col customWidth="1" min="6" max="6" width="35.38"/>
+    <col customWidth="1" min="6" max="6" width="47.63"/>
     <col customWidth="1" min="7" max="7" width="36.38"/>
     <col customWidth="1" min="8" max="8" width="18.13"/>
   </cols>
@@ -37280,7 +38682,9 @@
       <c r="G93" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="H93" s="9"/>
+      <c r="H93" s="11" t="s">
+        <v>202</v>
+      </c>
       <c r="I93" s="9"/>
       <c r="J93" s="9"/>
       <c r="K93" s="9"/>
@@ -37558,14 +38962,14 @@
         <v>external</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G100" s="9"/>
       <c r="H100" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I100" s="9"/>
       <c r="J100" s="9"/>
@@ -37604,13 +39008,13 @@
         <v>implicit</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H101" s="9"/>
       <c r="I101" s="9"/>
@@ -37851,10 +39255,10 @@
         <v>explicit</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
@@ -37895,10 +39299,10 @@
         <v>explicit</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
@@ -37939,16 +39343,16 @@
         <v>external</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G109" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="H109" s="11" t="s">
         <v>214</v>
-      </c>
-      <c r="H109" s="11" t="s">
-        <v>213</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="9"/>
@@ -37987,13 +39391,13 @@
         <v>explicit</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G110" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H110" s="9"/>
       <c r="I110" s="9"/>
@@ -38074,13 +39478,13 @@
         <v>implicit</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G112" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H112" s="9"/>
       <c r="I112" s="9"/>
@@ -38120,10 +39524,10 @@
         <v>explicit</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
@@ -38164,10 +39568,10 @@
         <v>explicit</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
@@ -38208,10 +39612,10 @@
         <v>explicit</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
@@ -38813,13 +40217,13 @@
         <v>explicit</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G130" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H130" s="9"/>
       <c r="I130" s="9"/>
@@ -38859,13 +40263,13 @@
         <v>explicit</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G131" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H131" s="9"/>
       <c r="I131" s="9"/>
@@ -38905,16 +40309,16 @@
         <v>external</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G132" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I132" s="9"/>
       <c r="J132" s="9"/>
@@ -38953,13 +40357,13 @@
         <v>implicit</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G133" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H133" s="9"/>
       <c r="I133" s="9"/>
@@ -39080,13 +40484,13 @@
         <v>explicit</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G136" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H136" s="9"/>
       <c r="I136" s="9"/>
@@ -39166,10 +40570,10 @@
         <v>explicit</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
@@ -39771,10 +41175,10 @@
         <v>explicit</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F153" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
@@ -39815,13 +41219,13 @@
         <v>explicit</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G154" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H154" s="9"/>
       <c r="I154" s="9"/>
@@ -39861,16 +41265,16 @@
         <v>external</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G155" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H155" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I155" s="9"/>
       <c r="J155" s="9"/>
@@ -39909,13 +41313,13 @@
         <v>explicit</v>
       </c>
       <c r="E156" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F156" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G156" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H156" s="9"/>
       <c r="I156" s="9"/>
@@ -40036,10 +41440,10 @@
         <v>explicit</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F159" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
@@ -40080,10 +41484,10 @@
         <v>explicit</v>
       </c>
       <c r="E160" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F160" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
@@ -40124,10 +41528,10 @@
         <v>explicit</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F161" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
@@ -40729,10 +42133,10 @@
         <v>explicit</v>
       </c>
       <c r="E176" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="9"/>
@@ -40773,13 +42177,13 @@
         <v>explicit</v>
       </c>
       <c r="E177" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="F177" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="F177" s="5" t="s">
-        <v>264</v>
-      </c>
       <c r="G177" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H177" s="9"/>
       <c r="I177" s="9"/>
@@ -40819,16 +42223,16 @@
         <v>external</v>
       </c>
       <c r="E178" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H178" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I178" s="9"/>
       <c r="J178" s="9"/>
@@ -40867,13 +42271,13 @@
         <v>implicit</v>
       </c>
       <c r="E179" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H179" s="9"/>
       <c r="I179" s="9"/>
@@ -40954,13 +42358,13 @@
         <v>implicit</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F181" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G181" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H181" s="9"/>
       <c r="I181" s="9"/>
@@ -41000,10 +42404,10 @@
         <v>explicit</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F182" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
@@ -41044,10 +42448,10 @@
         <v>explicit</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F183" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
@@ -41088,10 +42492,10 @@
         <v>explicit</v>
       </c>
       <c r="E184" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F184" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
@@ -41693,10 +43097,10 @@
         <v>explicit</v>
       </c>
       <c r="E199" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F199" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
@@ -41737,13 +43141,13 @@
         <v>explicit</v>
       </c>
       <c r="E200" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F200" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="F200" s="11" t="s">
-        <v>283</v>
-      </c>
       <c r="G200" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H200" s="9"/>
       <c r="I200" s="9"/>
@@ -41783,13 +43187,13 @@
         <v>implicit</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F201" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G201" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H201" s="9"/>
       <c r="I201" s="9"/>
@@ -41869,10 +43273,10 @@
         <v>implicit</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F203" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
@@ -41954,10 +43358,10 @@
         <v>explicit</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F205" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
@@ -42038,10 +43442,10 @@
         <v>explicit</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F207" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
@@ -42162,13 +43566,13 @@
         <v>implicit</v>
       </c>
       <c r="E210" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F210" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G210" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H210" s="9"/>
       <c r="I210" s="9"/>
@@ -42288,13 +43692,13 @@
         <v>implicit</v>
       </c>
       <c r="E213" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="F213" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="G213" s="11" t="s">
         <v>298</v>
-      </c>
-      <c r="F213" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="G213" s="11" t="s">
-        <v>297</v>
       </c>
       <c r="H213" s="9"/>
       <c r="I213" s="9"/>
@@ -42334,13 +43738,13 @@
         <v>implicit</v>
       </c>
       <c r="E214" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F214" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G214" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H214" s="9"/>
       <c r="I214" s="9"/>
@@ -42501,13 +43905,13 @@
         <v>explicit</v>
       </c>
       <c r="E218" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F218" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G218" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H218" s="9"/>
       <c r="I218" s="9"/>
@@ -42547,10 +43951,10 @@
         <v>explicit</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F219" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
@@ -42591,13 +43995,13 @@
         <v>explicit</v>
       </c>
       <c r="E220" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G220" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H220" s="9"/>
       <c r="I220" s="9"/>
@@ -42637,13 +44041,13 @@
         <v>implicit</v>
       </c>
       <c r="E221" s="15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G221" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H221" s="9"/>
       <c r="I221" s="9"/>
@@ -42843,10 +44247,10 @@
         <v>explicit</v>
       </c>
       <c r="E226" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
@@ -42968,10 +44372,10 @@
         <v>explicit</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F229" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
@@ -43012,10 +44416,10 @@
         <v>explicit</v>
       </c>
       <c r="E230" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
@@ -43056,14 +44460,14 @@
         <v>external</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G231" s="11"/>
       <c r="H231" s="11" t="s">
-        <v>321</v>
+        <v>202</v>
       </c>
       <c r="I231" s="9"/>
       <c r="J231" s="9"/>
@@ -44179,10 +45583,16 @@
         <f t="array" ref="D257">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A256)-1, 23)+1, INT((ROW(A256)-1)/23)+1)</f>
         <v>external</v>
       </c>
-      <c r="E257" s="9"/>
-      <c r="F257" s="9"/>
+      <c r="E257" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="F257" s="11" t="s">
+        <v>346</v>
+      </c>
       <c r="G257" s="9"/>
-      <c r="H257" s="9"/>
+      <c r="H257" s="11" t="s">
+        <v>347</v>
+      </c>
       <c r="I257" s="9"/>
       <c r="J257" s="9"/>
       <c r="K257" s="9"/>
@@ -44260,13 +45670,13 @@
         <v>implicit</v>
       </c>
       <c r="E259" s="10" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F259" s="11" t="s">
         <v>343</v>
       </c>
       <c r="G259" s="11" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H259" s="9"/>
       <c r="I259" s="9"/>
@@ -44306,13 +45716,13 @@
         <v>explicit</v>
       </c>
       <c r="E260" s="10" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G260" s="11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="H260" s="9"/>
       <c r="I260" s="9"/>
@@ -44352,10 +45762,10 @@
         <v>explicit</v>
       </c>
       <c r="E261" s="10" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
@@ -44396,13 +45806,13 @@
         <v>implicit</v>
       </c>
       <c r="E262" s="10" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="G262" s="11" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H262" s="9"/>
       <c r="I262" s="9"/>
@@ -44443,14 +45853,14 @@
         <v>external</v>
       </c>
       <c r="E263" s="10" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G263" s="9"/>
       <c r="H263" s="11" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I263" s="9"/>
       <c r="J263" s="9"/>
@@ -44489,10 +45899,10 @@
         <v>explicit</v>
       </c>
       <c r="E264" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
@@ -44533,13 +45943,13 @@
         <v>explicit</v>
       </c>
       <c r="E265" s="10" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F265" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G265" s="11" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H265" s="9"/>
       <c r="I265" s="9"/>
@@ -44579,10 +45989,10 @@
         <v>explicit</v>
       </c>
       <c r="E266" s="15" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
@@ -44623,13 +46033,13 @@
         <v>explicit</v>
       </c>
       <c r="E267" s="10" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G267" s="11" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H267" s="9"/>
       <c r="I267" s="9"/>
@@ -44829,10 +46239,10 @@
         <v>explicit</v>
       </c>
       <c r="E272" s="10" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
@@ -44874,10 +46284,10 @@
         <v>not implemented</v>
       </c>
       <c r="E273" s="10" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
@@ -45038,10 +46448,10 @@
         <v>explicit</v>
       </c>
       <c r="E277" s="10" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F277" s="11" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
@@ -45122,13 +46532,13 @@
         <v>implicit</v>
       </c>
       <c r="E279" s="10" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G279" s="11" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H279" s="9"/>
       <c r="I279" s="9"/>
@@ -45248,13 +46658,13 @@
         <v>implicit</v>
       </c>
       <c r="E282" s="10" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G282" s="11" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H282" s="9"/>
       <c r="I282" s="9"/>
@@ -45294,10 +46704,10 @@
         <v>explicit</v>
       </c>
       <c r="E283" s="10" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
@@ -45419,16 +46829,16 @@
         <v>external</v>
       </c>
       <c r="E286" s="10" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G286" s="11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="H286" s="11" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I286" s="9"/>
       <c r="J286" s="9"/>
@@ -45467,10 +46877,10 @@
         <v>explicit</v>
       </c>
       <c r="E287" s="10" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F287" s="11" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
@@ -45511,13 +46921,13 @@
         <v>explicit</v>
       </c>
       <c r="E288" s="17" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G288" s="11" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="H288" s="9"/>
       <c r="I288" s="9"/>
@@ -45557,16 +46967,16 @@
         <v>external</v>
       </c>
       <c r="E289" s="10" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F289" s="11" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G289" s="11" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H289" s="11" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I289" s="9"/>
       <c r="J289" s="9"/>
@@ -45605,10 +47015,10 @@
         <v>explicit</v>
       </c>
       <c r="E290" s="15" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
@@ -45809,10 +47219,10 @@
         <v>explicit</v>
       </c>
       <c r="E295" s="10" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
@@ -45934,10 +47344,10 @@
         <v>explicit</v>
       </c>
       <c r="E298" s="10" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
@@ -45978,10 +47388,10 @@
         <v>explicit</v>
       </c>
       <c r="E299" s="10" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F299" s="11" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
@@ -46102,13 +47512,13 @@
         <v>implicit</v>
       </c>
       <c r="E302" s="10" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G302" s="11" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H302" s="9"/>
       <c r="I302" s="9"/>
@@ -46148,14 +47558,14 @@
         <v>external</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G303" s="9"/>
       <c r="H303" s="11" t="s">
-        <v>408</v>
+        <v>347</v>
       </c>
       <c r="I303" s="9"/>
       <c r="J303" s="9"/>
@@ -46234,13 +47644,13 @@
         <v>implicit</v>
       </c>
       <c r="E305" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G305" s="11" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H305" s="9"/>
       <c r="I305" s="9"/>
@@ -46280,10 +47690,10 @@
         <v>external</v>
       </c>
       <c r="E306" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G306" s="9"/>
       <c r="H306" s="11" t="s">
@@ -46326,10 +47736,10 @@
         <v>external</v>
       </c>
       <c r="E307" s="10" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F307" s="11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G307" s="9"/>
       <c r="H307" s="11" t="s">
@@ -46372,13 +47782,13 @@
         <v>implicit</v>
       </c>
       <c r="E308" s="10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G308" s="11" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H308" s="9"/>
       <c r="I308" s="9"/>
@@ -46419,16 +47829,16 @@
         <v>external</v>
       </c>
       <c r="E309" s="10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F309" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G309" s="11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H309" s="11" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I309" s="9"/>
       <c r="J309" s="9"/>
@@ -46467,10 +47877,10 @@
         <v>external</v>
       </c>
       <c r="E310" s="10" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G310" s="9"/>
       <c r="H310" s="11" t="s">
@@ -46513,10 +47923,10 @@
         <v>external</v>
       </c>
       <c r="E311" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G311" s="9"/>
       <c r="H311" s="11" t="s">
@@ -46559,13 +47969,13 @@
         <v>external</v>
       </c>
       <c r="E312" s="10" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G312" s="11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H312" s="11" t="s">
         <v>31</v>
@@ -46607,10 +48017,10 @@
         <v>external</v>
       </c>
       <c r="E313" s="10" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G313" s="9"/>
       <c r="H313" s="11" t="s">
@@ -46813,16 +48223,16 @@
         <v>external</v>
       </c>
       <c r="E318" s="10" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F318" s="11" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G318" s="11" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H318" s="11" t="s">
-        <v>408</v>
+        <v>347</v>
       </c>
       <c r="I318" s="9"/>
       <c r="J318" s="9"/>
@@ -46982,16 +48392,16 @@
         <v>external</v>
       </c>
       <c r="E322" s="10" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G322" s="11" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H322" s="11" t="s">
-        <v>408</v>
+        <v>347</v>
       </c>
       <c r="I322" s="9"/>
       <c r="J322" s="9"/>
@@ -47030,16 +48440,16 @@
         <v>external</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G323" s="11" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H323" s="11" t="s">
-        <v>408</v>
+        <v>347</v>
       </c>
       <c r="I323" s="9"/>
       <c r="J323" s="9"/>
@@ -47117,9 +48527,15 @@
         <f t="array" ref="D325">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A324)-1, 23)+1, INT((ROW(A324)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E325" s="9"/>
-      <c r="F325" s="9"/>
-      <c r="G325" s="9"/>
+      <c r="E325" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="F325" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="G325" s="11" t="s">
+        <v>438</v>
+      </c>
       <c r="H325" s="9"/>
       <c r="I325" s="9"/>
       <c r="J325" s="9"/>
@@ -47197,8 +48613,12 @@
         <f t="array" ref="D327">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A326)-1, 23)+1, INT((ROW(A326)-1)/23)+1)</f>
         <v>explicit</v>
       </c>
-      <c r="E327" s="9"/>
-      <c r="F327" s="9"/>
+      <c r="E327" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="F327" s="11" t="s">
+        <v>440</v>
+      </c>
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="9"/>
@@ -47237,9 +48657,15 @@
         <f t="array" ref="D328">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A327)-1, 23)+1, INT((ROW(A327)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E328" s="9"/>
-      <c r="F328" s="9"/>
-      <c r="G328" s="9"/>
+      <c r="E328" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="F328" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="G328" s="11" t="s">
+        <v>443</v>
+      </c>
       <c r="H328" s="9"/>
       <c r="I328" s="9"/>
       <c r="J328" s="9"/>
@@ -47277,9 +48703,15 @@
         <f t="array" ref="D329">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A328)-1, 23)+1, INT((ROW(A328)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E329" s="9"/>
-      <c r="F329" s="9"/>
-      <c r="G329" s="9"/>
+      <c r="E329" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="F329" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="G329" s="11" t="s">
+        <v>446</v>
+      </c>
       <c r="H329" s="9"/>
       <c r="I329" s="9"/>
       <c r="J329" s="9"/>
@@ -47317,10 +48749,18 @@
         <f t="array" ref="D330">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A329)-1, 23)+1, INT((ROW(A329)-1)/23)+1)</f>
         <v>external</v>
       </c>
-      <c r="E330" s="9"/>
-      <c r="F330" s="9"/>
-      <c r="G330" s="9"/>
-      <c r="H330" s="9"/>
+      <c r="E330" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="F330" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="G330" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="H330" s="11" t="s">
+        <v>205</v>
+      </c>
       <c r="I330" s="9"/>
       <c r="J330" s="9"/>
       <c r="K330" s="9"/>
@@ -47357,9 +48797,15 @@
         <f t="array" ref="D331">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A330)-1, 23)+1, INT((ROW(A330)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E331" s="9"/>
-      <c r="F331" s="9"/>
-      <c r="G331" s="9"/>
+      <c r="E331" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="F331" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="G331" s="11" t="s">
+        <v>452</v>
+      </c>
       <c r="H331" s="9"/>
       <c r="I331" s="9"/>
       <c r="J331" s="9"/>
@@ -47438,8 +48884,12 @@
         <f t="array" ref="D333">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A332)-1, 23)+1, INT((ROW(A332)-1)/23)+1)</f>
         <v>explicit</v>
       </c>
-      <c r="E333" s="9"/>
-      <c r="F333" s="9"/>
+      <c r="E333" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="F333" s="11" t="s">
+        <v>454</v>
+      </c>
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="9"/>
@@ -47478,8 +48928,12 @@
         <f t="array" ref="D334">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A333)-1, 23)+1, INT((ROW(A333)-1)/23)+1)</f>
         <v>explicit</v>
       </c>
-      <c r="E334" s="9"/>
-      <c r="F334" s="9"/>
+      <c r="E334" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="F334" s="11" t="s">
+        <v>456</v>
+      </c>
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="9"/>
@@ -47518,8 +48972,12 @@
         <f t="array" ref="D335">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A334)-1, 23)+1, INT((ROW(A334)-1)/23)+1)</f>
         <v>explicit</v>
       </c>
-      <c r="E335" s="9"/>
-      <c r="F335" s="9"/>
+      <c r="E335" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="F335" s="11" t="s">
+        <v>458</v>
+      </c>
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="9"/>
@@ -47558,9 +49016,15 @@
         <f t="array" ref="D336">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A335)-1, 23)+1, INT((ROW(A335)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E336" s="9"/>
-      <c r="F336" s="9"/>
-      <c r="G336" s="9"/>
+      <c r="E336" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="F336" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="G336" s="11" t="s">
+        <v>461</v>
+      </c>
       <c r="H336" s="9"/>
       <c r="I336" s="9"/>
       <c r="J336" s="9"/>
@@ -47758,8 +49222,12 @@
         <f t="array" ref="D341">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A340)-1, 23)+1, INT((ROW(A340)-1)/23)+1)</f>
         <v>explicit</v>
       </c>
-      <c r="E341" s="9"/>
-      <c r="F341" s="9"/>
+      <c r="E341" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="F341" s="11" t="s">
+        <v>463</v>
+      </c>
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="9"/>
@@ -47879,9 +49347,15 @@
         <f t="array" ref="D344">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A343)-1, 23)+1, INT((ROW(A343)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E344" s="9"/>
-      <c r="F344" s="9"/>
-      <c r="G344" s="9"/>
+      <c r="E344" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="F344" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="G344" s="11" t="s">
+        <v>466</v>
+      </c>
       <c r="H344" s="9"/>
       <c r="I344" s="9"/>
       <c r="J344" s="9"/>
@@ -47919,10 +49393,18 @@
         <f t="array" ref="D345">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A344)-1, 23)+1, INT((ROW(A344)-1)/23)+1)</f>
         <v>external</v>
       </c>
-      <c r="E345" s="9"/>
-      <c r="F345" s="9"/>
-      <c r="G345" s="9"/>
-      <c r="H345" s="9"/>
+      <c r="E345" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="F345" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="G345" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="H345" s="11" t="s">
+        <v>470</v>
+      </c>
       <c r="I345" s="9"/>
       <c r="J345" s="9"/>
       <c r="K345" s="9"/>
@@ -47959,10 +49441,18 @@
         <f t="array" ref="D346">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A345)-1, 23)+1, INT((ROW(A345)-1)/23)+1)</f>
         <v>external</v>
       </c>
-      <c r="E346" s="9"/>
-      <c r="F346" s="9"/>
-      <c r="G346" s="9"/>
-      <c r="H346" s="9"/>
+      <c r="E346" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="F346" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="G346" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="H346" s="11" t="s">
+        <v>474</v>
+      </c>
       <c r="I346" s="9"/>
       <c r="J346" s="9"/>
       <c r="K346" s="9"/>
@@ -48039,9 +49529,15 @@
         <f t="array" ref="D348">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A347)-1, 23)+1, INT((ROW(A347)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E348" s="9"/>
-      <c r="F348" s="9"/>
-      <c r="G348" s="9"/>
+      <c r="E348" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="F348" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="G348" s="11" t="s">
+        <v>477</v>
+      </c>
       <c r="H348" s="9"/>
       <c r="I348" s="9"/>
       <c r="J348" s="9"/>
@@ -48159,9 +49655,15 @@
         <f t="array" ref="D351">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A350)-1, 23)+1, INT((ROW(A350)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E351" s="9"/>
-      <c r="F351" s="9"/>
-      <c r="G351" s="9"/>
+      <c r="E351" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="F351" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="G351" s="11" t="s">
+        <v>479</v>
+      </c>
       <c r="H351" s="9"/>
       <c r="I351" s="9"/>
       <c r="J351" s="9"/>
@@ -48199,9 +49701,15 @@
         <f t="array" ref="D352">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A351)-1, 23)+1, INT((ROW(A351)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E352" s="9"/>
-      <c r="F352" s="9"/>
-      <c r="G352" s="9"/>
+      <c r="E352" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="F352" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="G352" s="11" t="s">
+        <v>482</v>
+      </c>
       <c r="H352" s="9"/>
       <c r="I352" s="9"/>
       <c r="J352" s="9"/>
@@ -48239,10 +49747,16 @@
         <f t="array" ref="D353">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A352)-1, 23)+1, INT((ROW(A352)-1)/23)+1)</f>
         <v>external</v>
       </c>
-      <c r="E353" s="9"/>
-      <c r="F353" s="9"/>
+      <c r="E353" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="F353" s="11" t="s">
+        <v>484</v>
+      </c>
       <c r="G353" s="9"/>
-      <c r="H353" s="9"/>
+      <c r="H353" s="11" t="s">
+        <v>205</v>
+      </c>
       <c r="I353" s="9"/>
       <c r="J353" s="9"/>
       <c r="K353" s="9"/>
@@ -48320,9 +49834,15 @@
         <f t="array" ref="D355">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A354)-1, 23)+1, INT((ROW(A354)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E355" s="9"/>
-      <c r="F355" s="9"/>
-      <c r="G355" s="9"/>
+      <c r="E355" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="F355" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="G355" s="11" t="s">
+        <v>487</v>
+      </c>
       <c r="H355" s="9"/>
       <c r="I355" s="9"/>
       <c r="J355" s="9"/>
@@ -48360,8 +49880,12 @@
         <f t="array" ref="D356">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A355)-1, 23)+1, INT((ROW(A355)-1)/23)+1)</f>
         <v>explicit</v>
       </c>
-      <c r="E356" s="9"/>
-      <c r="F356" s="9"/>
+      <c r="E356" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="F356" s="11" t="s">
+        <v>489</v>
+      </c>
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="9"/>
@@ -48400,9 +49924,15 @@
         <f t="array" ref="D357">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A356)-1, 23)+1, INT((ROW(A356)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E357" s="9"/>
-      <c r="F357" s="9"/>
-      <c r="G357" s="9"/>
+      <c r="E357" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="F357" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="G357" s="11" t="s">
+        <v>492</v>
+      </c>
       <c r="H357" s="9"/>
       <c r="I357" s="9"/>
       <c r="J357" s="9"/>
@@ -48440,10 +49970,16 @@
         <f t="array" ref="D358">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A357)-1, 23)+1, INT((ROW(A357)-1)/23)+1)</f>
         <v>external</v>
       </c>
-      <c r="E358" s="9"/>
-      <c r="F358" s="9"/>
+      <c r="E358" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="F358" s="11" t="s">
+        <v>494</v>
+      </c>
       <c r="G358" s="9"/>
-      <c r="H358" s="9"/>
+      <c r="H358" s="11" t="s">
+        <v>495</v>
+      </c>
       <c r="I358" s="9"/>
       <c r="J358" s="9"/>
       <c r="K358" s="9"/>
@@ -48480,9 +50016,15 @@
         <f t="array" ref="D359">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A358)-1, 23)+1, INT((ROW(A358)-1)/23)+1)</f>
         <v>implicit</v>
       </c>
-      <c r="E359" s="9"/>
-      <c r="F359" s="9"/>
-      <c r="G359" s="9"/>
+      <c r="E359" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="F359" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="G359" s="11" t="s">
+        <v>498</v>
+      </c>
       <c r="H359" s="9"/>
       <c r="I359" s="9"/>
       <c r="J359" s="9"/>
@@ -48680,10 +50222,16 @@
         <f t="array" ref="D364">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A363)-1, 23)+1, INT((ROW(A363)-1)/23)+1)</f>
         <v>external</v>
       </c>
-      <c r="E364" s="9"/>
-      <c r="F364" s="9"/>
+      <c r="E364" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="F364" s="11" t="s">
+        <v>500</v>
+      </c>
       <c r="G364" s="9"/>
-      <c r="H364" s="9"/>
+      <c r="H364" s="11" t="s">
+        <v>501</v>
+      </c>
       <c r="I364" s="9"/>
       <c r="J364" s="9"/>
       <c r="K364" s="9"/>
@@ -48841,10 +50389,16 @@
         <f t="array" ref="D368">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A367)-1, 23)+1, INT((ROW(A367)-1)/23)+1)</f>
         <v>external</v>
       </c>
-      <c r="E368" s="9"/>
-      <c r="F368" s="9"/>
+      <c r="E368" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="F368" s="11" t="s">
+        <v>503</v>
+      </c>
       <c r="G368" s="9"/>
-      <c r="H368" s="9"/>
+      <c r="H368" s="11" t="s">
+        <v>504</v>
+      </c>
       <c r="I368" s="9"/>
       <c r="J368" s="9"/>
       <c r="K368" s="9"/>
@@ -48881,10 +50435,18 @@
         <f t="array" ref="D369">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A368)-1, 23)+1, INT((ROW(A368)-1)/23)+1)</f>
         <v>external</v>
       </c>
-      <c r="E369" s="9"/>
-      <c r="F369" s="9"/>
-      <c r="G369" s="9"/>
-      <c r="H369" s="9"/>
+      <c r="E369" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="F369" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="G369" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="H369" s="11" t="s">
+        <v>176</v>
+      </c>
       <c r="I369" s="9"/>
       <c r="J369" s="9"/>
       <c r="K369" s="9"/>
@@ -48945,13 +50507,31 @@
       <c r="Z370" s="9"/>
     </row>
     <row r="371">
-      <c r="A371" s="9"/>
-      <c r="B371" s="9"/>
-      <c r="C371" s="9"/>
-      <c r="D371" s="9"/>
-      <c r="E371" s="9"/>
-      <c r="F371" s="9"/>
-      <c r="G371" s="9"/>
+      <c r="A371" s="5" t="str">
+        <f t="array" ref="A371">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A370)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B371" s="5" t="str">
+        <f t="array" ref="B371">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B370)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C371" s="5" t="str">
+        <f t="array" ref="C371">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A370)-1, 23)+1)</f>
+        <v>Experiment Manager</v>
+      </c>
+      <c r="D371" s="5" t="str">
+        <f t="array" ref="D371">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A370)-1, 23)+1, INT((ROW(A370)-1)/23)+1)</f>
+        <v>implicit</v>
+      </c>
+      <c r="E371" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="F371" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="G371" s="11" t="s">
+        <v>510</v>
+      </c>
       <c r="H371" s="9"/>
       <c r="I371" s="9"/>
       <c r="J371" s="9"/>
@@ -48973,10 +50553,22 @@
       <c r="Z371" s="9"/>
     </row>
     <row r="372">
-      <c r="A372" s="9"/>
-      <c r="B372" s="9"/>
-      <c r="C372" s="9"/>
-      <c r="D372" s="9"/>
+      <c r="A372" s="5" t="str">
+        <f t="array" ref="A372">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A371)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B372" s="5" t="str">
+        <f t="array" ref="B372">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B371)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C372" s="5" t="str">
+        <f t="array" ref="C372">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A371)-1, 23)+1)</f>
+        <v>Hyperparameter Tuner</v>
+      </c>
+      <c r="D372" s="5" t="str">
+        <f t="array" ref="D372">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A371)-1, 23)+1, INT((ROW(A371)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E372" s="9"/>
       <c r="F372" s="9"/>
       <c r="G372" s="9"/>
@@ -49001,10 +50593,22 @@
       <c r="Z372" s="9"/>
     </row>
     <row r="373">
-      <c r="A373" s="9"/>
-      <c r="B373" s="9"/>
-      <c r="C373" s="9"/>
-      <c r="D373" s="9"/>
+      <c r="A373" s="5" t="str">
+        <f t="array" ref="A373">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A372)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B373" s="5" t="str">
+        <f t="array" ref="B373">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B372)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C373" s="5" t="str">
+        <f t="array" ref="C373">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A372)-1, 23)+1)</f>
+        <v>Benchmark Manager</v>
+      </c>
+      <c r="D373" s="5" t="str">
+        <f t="array" ref="D373">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A372)-1, 23)+1, INT((ROW(A372)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E373" s="9"/>
       <c r="F373" s="9"/>
       <c r="G373" s="9"/>
@@ -49029,13 +50633,31 @@
       <c r="Z373" s="9"/>
     </row>
     <row r="374">
-      <c r="A374" s="9"/>
-      <c r="B374" s="9"/>
-      <c r="C374" s="9"/>
-      <c r="D374" s="9"/>
-      <c r="E374" s="9"/>
-      <c r="F374" s="9"/>
-      <c r="G374" s="9"/>
+      <c r="A374" s="5" t="str">
+        <f t="array" ref="A374">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A373)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B374" s="5" t="str">
+        <f t="array" ref="B374">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B373)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C374" s="5" t="str">
+        <f t="array" ref="C374">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A373)-1, 23)+1)</f>
+        <v>Framework Orchestrator</v>
+      </c>
+      <c r="D374" s="5" t="str">
+        <f t="array" ref="D374">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A373)-1, 23)+1, INT((ROW(A373)-1)/23)+1)</f>
+        <v>implicit</v>
+      </c>
+      <c r="E374" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="F374" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="G374" s="11" t="s">
+        <v>512</v>
+      </c>
       <c r="H374" s="9"/>
       <c r="I374" s="9"/>
       <c r="J374" s="9"/>
@@ -49057,13 +50679,31 @@
       <c r="Z374" s="9"/>
     </row>
     <row r="375">
-      <c r="A375" s="9"/>
-      <c r="B375" s="9"/>
-      <c r="C375" s="9"/>
-      <c r="D375" s="9"/>
-      <c r="E375" s="9"/>
-      <c r="F375" s="9"/>
-      <c r="G375" s="9"/>
+      <c r="A375" s="5" t="str">
+        <f t="array" ref="A375">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A374)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B375" s="5" t="str">
+        <f t="array" ref="B375">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B374)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C375" s="5" t="str">
+        <f t="array" ref="C375">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A374)-1, 23)+1)</f>
+        <v>Lifecycle Manager</v>
+      </c>
+      <c r="D375" s="5" t="str">
+        <f t="array" ref="D375">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A374)-1, 23)+1, INT((ROW(A374)-1)/23)+1)</f>
+        <v>implicit</v>
+      </c>
+      <c r="E375" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="F375" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="G375" s="11" t="s">
+        <v>515</v>
+      </c>
       <c r="H375" s="9"/>
       <c r="I375" s="9"/>
       <c r="J375" s="9"/>
@@ -49085,14 +50725,32 @@
       <c r="Z375" s="9"/>
     </row>
     <row r="376">
-      <c r="A376" s="9"/>
-      <c r="B376" s="9"/>
-      <c r="C376" s="9"/>
-      <c r="D376" s="9"/>
-      <c r="E376" s="9"/>
-      <c r="F376" s="9"/>
+      <c r="A376" s="5" t="str">
+        <f t="array" ref="A376">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A375)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B376" s="5" t="str">
+        <f t="array" ref="B376">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B375)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C376" s="5" t="str">
+        <f t="array" ref="C376">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A375)-1, 23)+1)</f>
+        <v>Configuration Manager</v>
+      </c>
+      <c r="D376" s="5" t="str">
+        <f t="array" ref="D376">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A375)-1, 23)+1, INT((ROW(A375)-1)/23)+1)</f>
+        <v>external</v>
+      </c>
+      <c r="E376" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="F376" s="11" t="s">
+        <v>517</v>
+      </c>
       <c r="G376" s="9"/>
-      <c r="H376" s="9"/>
+      <c r="H376" s="11" t="s">
+        <v>518</v>
+      </c>
       <c r="I376" s="9"/>
       <c r="J376" s="9"/>
       <c r="K376" s="9"/>
@@ -49113,10 +50771,22 @@
       <c r="Z376" s="9"/>
     </row>
     <row r="377">
-      <c r="A377" s="9"/>
-      <c r="B377" s="9"/>
-      <c r="C377" s="9"/>
-      <c r="D377" s="9"/>
+      <c r="A377" s="5" t="str">
+        <f t="array" ref="A377">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A376)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B377" s="5" t="str">
+        <f t="array" ref="B377">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B376)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C377" s="5" t="str">
+        <f t="array" ref="C377">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A376)-1, 23)+1)</f>
+        <v>Multi-Agent Coordinator</v>
+      </c>
+      <c r="D377" s="5" t="str">
+        <f t="array" ref="D377">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A376)-1, 23)+1, INT((ROW(A376)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E377" s="9"/>
       <c r="F377" s="9"/>
       <c r="G377" s="9"/>
@@ -49141,10 +50811,23 @@
       <c r="Z377" s="9"/>
     </row>
     <row r="378">
-      <c r="A378" s="9"/>
-      <c r="B378" s="9"/>
-      <c r="C378" s="9"/>
-      <c r="D378" s="9"/>
+      <c r="A378" s="5" t="str">
+        <f t="array" ref="A378">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A377)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B378" s="5" t="str">
+        <f t="array" ref="B378">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B377)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C378" s="5" t="str">
+        <f t="array" ref="C378">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A377)-1, 23)+1)</f>
+        <v>Distributed Execution 
+Coordinator</v>
+      </c>
+      <c r="D378" s="5" t="str">
+        <f t="array" ref="D378">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A377)-1, 23)+1, INT((ROW(A377)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E378" s="9"/>
       <c r="F378" s="9"/>
       <c r="G378" s="9"/>
@@ -49169,13 +50852,31 @@
       <c r="Z378" s="9"/>
     </row>
     <row r="379">
-      <c r="A379" s="9"/>
-      <c r="B379" s="9"/>
-      <c r="C379" s="9"/>
-      <c r="D379" s="9"/>
-      <c r="E379" s="9"/>
-      <c r="F379" s="9"/>
-      <c r="G379" s="9"/>
+      <c r="A379" s="5" t="str">
+        <f t="array" ref="A379">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A378)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B379" s="5" t="str">
+        <f t="array" ref="B379">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B378)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C379" s="5" t="str">
+        <f t="array" ref="C379">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A378)-1, 23)+1)</f>
+        <v>Agent</v>
+      </c>
+      <c r="D379" s="5" t="str">
+        <f t="array" ref="D379">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A378)-1, 23)+1, INT((ROW(A378)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E379" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="F379" s="11" t="s">
+        <v>520</v>
+      </c>
+      <c r="G379" s="11" t="s">
+        <v>521</v>
+      </c>
       <c r="H379" s="9"/>
       <c r="I379" s="9"/>
       <c r="J379" s="9"/>
@@ -49197,13 +50898,31 @@
       <c r="Z379" s="9"/>
     </row>
     <row r="380">
-      <c r="A380" s="9"/>
-      <c r="B380" s="9"/>
-      <c r="C380" s="9"/>
-      <c r="D380" s="9"/>
-      <c r="E380" s="9"/>
-      <c r="F380" s="9"/>
-      <c r="G380" s="9"/>
+      <c r="A380" s="5" t="str">
+        <f t="array" ref="A380">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A379)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B380" s="5" t="str">
+        <f t="array" ref="B380">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B379)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C380" s="5" t="str">
+        <f t="array" ref="C380">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A379)-1, 23)+1)</f>
+        <v>Function Approximator</v>
+      </c>
+      <c r="D380" s="5" t="str">
+        <f t="array" ref="D380">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A379)-1, 23)+1, INT((ROW(A379)-1)/23)+1)</f>
+        <v>implicit</v>
+      </c>
+      <c r="E380" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="F380" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="G380" s="11" t="s">
+        <v>524</v>
+      </c>
       <c r="H380" s="9"/>
       <c r="I380" s="9"/>
       <c r="J380" s="9"/>
@@ -49225,12 +50944,28 @@
       <c r="Z380" s="9"/>
     </row>
     <row r="381">
-      <c r="A381" s="9"/>
-      <c r="B381" s="9"/>
-      <c r="C381" s="9"/>
-      <c r="D381" s="9"/>
-      <c r="E381" s="9"/>
-      <c r="F381" s="9"/>
+      <c r="A381" s="5" t="str">
+        <f t="array" ref="A381">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A380)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B381" s="5" t="str">
+        <f t="array" ref="B381">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B380)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C381" s="5" t="str">
+        <f t="array" ref="C381">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A380)-1, 23)+1)</f>
+        <v>Buffer</v>
+      </c>
+      <c r="D381" s="5" t="str">
+        <f t="array" ref="D381">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A380)-1, 23)+1, INT((ROW(A380)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E381" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="F381" s="11" t="s">
+        <v>526</v>
+      </c>
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="9"/>
@@ -49253,13 +50988,31 @@
       <c r="Z381" s="9"/>
     </row>
     <row r="382">
-      <c r="A382" s="9"/>
-      <c r="B382" s="9"/>
-      <c r="C382" s="9"/>
-      <c r="D382" s="9"/>
-      <c r="E382" s="9"/>
-      <c r="F382" s="9"/>
-      <c r="G382" s="9"/>
+      <c r="A382" s="5" t="str">
+        <f t="array" ref="A382">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A381)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B382" s="5" t="str">
+        <f t="array" ref="B382">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B381)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C382" s="5" t="str">
+        <f t="array" ref="C382">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A381)-1, 23)+1)</f>
+        <v>Learner</v>
+      </c>
+      <c r="D382" s="5" t="str">
+        <f t="array" ref="D382">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A381)-1, 23)+1, INT((ROW(A381)-1)/23)+1)</f>
+        <v>implicit</v>
+      </c>
+      <c r="E382" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="F382" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="G382" s="11" t="s">
+        <v>529</v>
+      </c>
       <c r="H382" s="9"/>
       <c r="I382" s="9"/>
       <c r="J382" s="9"/>
@@ -49281,10 +51034,22 @@
       <c r="Z382" s="9"/>
     </row>
     <row r="383">
-      <c r="A383" s="9"/>
-      <c r="B383" s="9"/>
-      <c r="C383" s="9"/>
-      <c r="D383" s="9"/>
+      <c r="A383" s="5" t="str">
+        <f t="array" ref="A383">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A382)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B383" s="5" t="str">
+        <f t="array" ref="B383">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B382)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C383" s="5" t="str">
+        <f t="array" ref="C383">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A382)-1, 23)+1)</f>
+        <v>Environment</v>
+      </c>
+      <c r="D383" s="5" t="str">
+        <f t="array" ref="D383">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A382)-1, 23)+1, INT((ROW(A382)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E383" s="9"/>
       <c r="F383" s="9"/>
       <c r="G383" s="9"/>
@@ -49309,10 +51074,22 @@
       <c r="Z383" s="9"/>
     </row>
     <row r="384">
-      <c r="A384" s="9"/>
-      <c r="B384" s="9"/>
-      <c r="C384" s="9"/>
-      <c r="D384" s="9"/>
+      <c r="A384" s="5" t="str">
+        <f t="array" ref="A384">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A383)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B384" s="5" t="str">
+        <f t="array" ref="B384">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B383)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C384" s="5" t="str">
+        <f t="array" ref="C384">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A383)-1, 23)+1)</f>
+        <v>Environment Core</v>
+      </c>
+      <c r="D384" s="5" t="str">
+        <f t="array" ref="D384">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A383)-1, 23)+1, INT((ROW(A383)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E384" s="9"/>
       <c r="F384" s="9"/>
       <c r="G384" s="9"/>
@@ -49337,10 +51114,22 @@
       <c r="Z384" s="9"/>
     </row>
     <row r="385">
-      <c r="A385" s="9"/>
-      <c r="B385" s="9"/>
-      <c r="C385" s="9"/>
-      <c r="D385" s="9"/>
+      <c r="A385" s="5" t="str">
+        <f t="array" ref="A385">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A384)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B385" s="5" t="str">
+        <f t="array" ref="B385">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B384)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C385" s="5" t="str">
+        <f t="array" ref="C385">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A384)-1, 23)+1)</f>
+        <v>Simulator</v>
+      </c>
+      <c r="D385" s="5" t="str">
+        <f t="array" ref="D385">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A384)-1, 23)+1, INT((ROW(A384)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E385" s="9"/>
       <c r="F385" s="9"/>
       <c r="G385" s="9"/>
@@ -49365,10 +51154,22 @@
       <c r="Z385" s="9"/>
     </row>
     <row r="386">
-      <c r="A386" s="9"/>
-      <c r="B386" s="9"/>
-      <c r="C386" s="9"/>
-      <c r="D386" s="9"/>
+      <c r="A386" s="5" t="str">
+        <f t="array" ref="A386">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A385)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B386" s="5" t="str">
+        <f t="array" ref="B386">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B385)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C386" s="5" t="str">
+        <f t="array" ref="C386">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A385)-1, 23)+1)</f>
+        <v>Simulator Adapter</v>
+      </c>
+      <c r="D386" s="5" t="str">
+        <f t="array" ref="D386">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A385)-1, 23)+1, INT((ROW(A385)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E386" s="9"/>
       <c r="F386" s="9"/>
       <c r="G386" s="9"/>
@@ -49393,12 +51194,28 @@
       <c r="Z386" s="9"/>
     </row>
     <row r="387">
-      <c r="A387" s="9"/>
-      <c r="B387" s="9"/>
-      <c r="C387" s="9"/>
-      <c r="D387" s="9"/>
-      <c r="E387" s="9"/>
-      <c r="F387" s="9"/>
+      <c r="A387" s="5" t="str">
+        <f t="array" ref="A387">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A386)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B387" s="5" t="str">
+        <f t="array" ref="B387">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B386)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C387" s="5" t="str">
+        <f t="array" ref="C387">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A386)-1, 23)+1)</f>
+        <v>Checkpoint Manager</v>
+      </c>
+      <c r="D387" s="5" t="str">
+        <f t="array" ref="D387">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A386)-1, 23)+1, INT((ROW(A386)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E387" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="F387" s="11" t="s">
+        <v>531</v>
+      </c>
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="9"/>
@@ -49421,10 +51238,23 @@
       <c r="Z387" s="9"/>
     </row>
     <row r="388">
-      <c r="A388" s="9"/>
-      <c r="B388" s="9"/>
-      <c r="C388" s="9"/>
-      <c r="D388" s="9"/>
+      <c r="A388" s="5" t="str">
+        <f t="array" ref="A388">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A387)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B388" s="5" t="str">
+        <f t="array" ref="B388">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B387)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C388" s="5" t="str">
+        <f t="array" ref="C388">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A387)-1, 23)+1)</f>
+        <v>Environment Parameter 
+Manager</v>
+      </c>
+      <c r="D388" s="5" t="str">
+        <f t="array" ref="D388">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A387)-1, 23)+1, INT((ROW(A387)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E388" s="9"/>
       <c r="F388" s="9"/>
       <c r="G388" s="9"/>
@@ -49449,10 +51279,22 @@
       <c r="Z388" s="9"/>
     </row>
     <row r="389">
-      <c r="A389" s="9"/>
-      <c r="B389" s="9"/>
-      <c r="C389" s="9"/>
-      <c r="D389" s="9"/>
+      <c r="A389" s="5" t="str">
+        <f t="array" ref="A389">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A388)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B389" s="5" t="str">
+        <f t="array" ref="B389">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B388)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C389" s="5" t="str">
+        <f t="array" ref="C389">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A388)-1, 23)+1)</f>
+        <v>Renderer</v>
+      </c>
+      <c r="D389" s="5" t="str">
+        <f t="array" ref="D389">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A388)-1, 23)+1, INT((ROW(A388)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E389" s="9"/>
       <c r="F389" s="9"/>
       <c r="G389" s="9"/>
@@ -49477,13 +51319,31 @@
       <c r="Z389" s="9"/>
     </row>
     <row r="390">
-      <c r="A390" s="9"/>
-      <c r="B390" s="9"/>
-      <c r="C390" s="9"/>
-      <c r="D390" s="9"/>
-      <c r="E390" s="9"/>
-      <c r="F390" s="9"/>
-      <c r="G390" s="9"/>
+      <c r="A390" s="5" t="str">
+        <f t="array" ref="A390">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A389)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B390" s="5" t="str">
+        <f t="array" ref="B390">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B389)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C390" s="5" t="str">
+        <f t="array" ref="C390">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A389)-1, 23)+1)</f>
+        <v>Recorder</v>
+      </c>
+      <c r="D390" s="5" t="str">
+        <f t="array" ref="D390">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A389)-1, 23)+1, INT((ROW(A389)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E390" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="F390" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="G390" s="11" t="s">
+        <v>534</v>
+      </c>
       <c r="H390" s="9"/>
       <c r="I390" s="9"/>
       <c r="J390" s="9"/>
@@ -49505,12 +51365,28 @@
       <c r="Z390" s="9"/>
     </row>
     <row r="391">
-      <c r="A391" s="9"/>
-      <c r="B391" s="9"/>
-      <c r="C391" s="9"/>
-      <c r="D391" s="9"/>
-      <c r="E391" s="9"/>
-      <c r="F391" s="9"/>
+      <c r="A391" s="5" t="str">
+        <f t="array" ref="A391">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A390)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B391" s="5" t="str">
+        <f t="array" ref="B391">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B390)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C391" s="5" t="str">
+        <f t="array" ref="C391">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A390)-1, 23)+1)</f>
+        <v>Logger</v>
+      </c>
+      <c r="D391" s="5" t="str">
+        <f t="array" ref="D391">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A390)-1, 23)+1, INT((ROW(A390)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E391" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="F391" s="11" t="s">
+        <v>536</v>
+      </c>
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="9"/>
@@ -49533,14 +51409,32 @@
       <c r="Z391" s="9"/>
     </row>
     <row r="392">
-      <c r="A392" s="9"/>
-      <c r="B392" s="9"/>
-      <c r="C392" s="9"/>
-      <c r="D392" s="9"/>
-      <c r="E392" s="9"/>
-      <c r="F392" s="9"/>
+      <c r="A392" s="5" t="str">
+        <f t="array" ref="A392">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A391)-1)/23)+1)</f>
+        <v>F17</v>
+      </c>
+      <c r="B392" s="5" t="str">
+        <f t="array" ref="B392">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B391)-1)/23)+1)</f>
+        <v>Dopamine</v>
+      </c>
+      <c r="C392" s="5" t="str">
+        <f t="array" ref="C392">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A391)-1, 23)+1)</f>
+        <v>Reporter</v>
+      </c>
+      <c r="D392" s="5" t="str">
+        <f t="array" ref="D392">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A391)-1, 23)+1, INT((ROW(A391)-1)/23)+1)</f>
+        <v>external</v>
+      </c>
+      <c r="E392" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="F392" s="11" t="s">
+        <v>538</v>
+      </c>
       <c r="G392" s="9"/>
-      <c r="H392" s="9"/>
+      <c r="H392" s="11" t="s">
+        <v>176</v>
+      </c>
       <c r="I392" s="9"/>
       <c r="J392" s="9"/>
       <c r="K392" s="9"/>
@@ -49561,10 +51455,22 @@
       <c r="Z392" s="9"/>
     </row>
     <row r="393">
-      <c r="A393" s="9"/>
-      <c r="B393" s="9"/>
-      <c r="C393" s="9"/>
-      <c r="D393" s="9"/>
+      <c r="A393" s="5" t="str">
+        <f t="array" ref="A393">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A392)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B393" s="5" t="str">
+        <f t="array" ref="B393">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B392)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C393" s="5" t="str">
+        <f t="array" ref="C393">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A392)-1, 23)+1)</f>
+        <v>Experiment Orchestrator</v>
+      </c>
+      <c r="D393" s="5" t="str">
+        <f t="array" ref="D393">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A392)-1, 23)+1, INT((ROW(A392)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E393" s="9"/>
       <c r="F393" s="9"/>
       <c r="G393" s="9"/>
@@ -49589,13 +51495,31 @@
       <c r="Z393" s="9"/>
     </row>
     <row r="394">
-      <c r="A394" s="9"/>
-      <c r="B394" s="9"/>
-      <c r="C394" s="9"/>
-      <c r="D394" s="9"/>
-      <c r="E394" s="9"/>
-      <c r="F394" s="9"/>
-      <c r="G394" s="9"/>
+      <c r="A394" s="5" t="str">
+        <f t="array" ref="A394">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A393)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B394" s="5" t="str">
+        <f t="array" ref="B394">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B393)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C394" s="5" t="str">
+        <f t="array" ref="C394">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A393)-1, 23)+1)</f>
+        <v>Experiment Manager</v>
+      </c>
+      <c r="D394" s="5" t="str">
+        <f t="array" ref="D394">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A393)-1, 23)+1, INT((ROW(A393)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E394" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="F394" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="G394" s="11" t="s">
+        <v>541</v>
+      </c>
       <c r="H394" s="9"/>
       <c r="I394" s="9"/>
       <c r="J394" s="9"/>
@@ -49617,10 +51541,22 @@
       <c r="Z394" s="9"/>
     </row>
     <row r="395">
-      <c r="A395" s="9"/>
-      <c r="B395" s="9"/>
-      <c r="C395" s="9"/>
-      <c r="D395" s="9"/>
+      <c r="A395" s="5" t="str">
+        <f t="array" ref="A395">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A394)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B395" s="5" t="str">
+        <f t="array" ref="B395">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B394)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C395" s="5" t="str">
+        <f t="array" ref="C395">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A394)-1, 23)+1)</f>
+        <v>Hyperparameter Tuner</v>
+      </c>
+      <c r="D395" s="5" t="str">
+        <f t="array" ref="D395">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A394)-1, 23)+1, INT((ROW(A394)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E395" s="9"/>
       <c r="F395" s="9"/>
       <c r="G395" s="9"/>
@@ -49645,10 +51581,22 @@
       <c r="Z395" s="9"/>
     </row>
     <row r="396">
-      <c r="A396" s="9"/>
-      <c r="B396" s="9"/>
-      <c r="C396" s="9"/>
-      <c r="D396" s="9"/>
+      <c r="A396" s="5" t="str">
+        <f t="array" ref="A396">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A395)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B396" s="5" t="str">
+        <f t="array" ref="B396">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B395)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C396" s="5" t="str">
+        <f t="array" ref="C396">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A395)-1, 23)+1)</f>
+        <v>Benchmark Manager</v>
+      </c>
+      <c r="D396" s="5" t="str">
+        <f t="array" ref="D396">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A395)-1, 23)+1, INT((ROW(A395)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E396" s="9"/>
       <c r="F396" s="9"/>
       <c r="G396" s="9"/>
@@ -49673,13 +51621,31 @@
       <c r="Z396" s="9"/>
     </row>
     <row r="397">
-      <c r="A397" s="9"/>
-      <c r="B397" s="9"/>
-      <c r="C397" s="9"/>
-      <c r="D397" s="9"/>
-      <c r="E397" s="9"/>
-      <c r="F397" s="9"/>
-      <c r="G397" s="9"/>
+      <c r="A397" s="5" t="str">
+        <f t="array" ref="A397">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A396)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B397" s="5" t="str">
+        <f t="array" ref="B397">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B396)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C397" s="5" t="str">
+        <f t="array" ref="C397">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A396)-1, 23)+1)</f>
+        <v>Framework Orchestrator</v>
+      </c>
+      <c r="D397" s="5" t="str">
+        <f t="array" ref="D397">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A396)-1, 23)+1, INT((ROW(A396)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E397" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="F397" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="G397" s="11" t="s">
+        <v>544</v>
+      </c>
       <c r="H397" s="9"/>
       <c r="I397" s="9"/>
       <c r="J397" s="9"/>
@@ -49701,13 +51667,31 @@
       <c r="Z397" s="9"/>
     </row>
     <row r="398">
-      <c r="A398" s="9"/>
-      <c r="B398" s="9"/>
-      <c r="C398" s="9"/>
-      <c r="D398" s="9"/>
-      <c r="E398" s="9"/>
-      <c r="F398" s="9"/>
-      <c r="G398" s="9"/>
+      <c r="A398" s="5" t="str">
+        <f t="array" ref="A398">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A397)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B398" s="5" t="str">
+        <f t="array" ref="B398">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B397)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C398" s="5" t="str">
+        <f t="array" ref="C398">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A397)-1, 23)+1)</f>
+        <v>Lifecycle Manager</v>
+      </c>
+      <c r="D398" s="5" t="str">
+        <f t="array" ref="D398">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A397)-1, 23)+1, INT((ROW(A397)-1)/23)+1)</f>
+        <v>implicit</v>
+      </c>
+      <c r="E398" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="F398" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="G398" s="11" t="s">
+        <v>547</v>
+      </c>
       <c r="H398" s="9"/>
       <c r="I398" s="9"/>
       <c r="J398" s="9"/>
@@ -49729,12 +51713,28 @@
       <c r="Z398" s="9"/>
     </row>
     <row r="399">
-      <c r="A399" s="9"/>
-      <c r="B399" s="9"/>
-      <c r="C399" s="9"/>
-      <c r="D399" s="9"/>
-      <c r="E399" s="9"/>
-      <c r="F399" s="9"/>
+      <c r="A399" s="5" t="str">
+        <f t="array" ref="A399">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A398)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B399" s="5" t="str">
+        <f t="array" ref="B399">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B398)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C399" s="5" t="str">
+        <f t="array" ref="C399">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A398)-1, 23)+1)</f>
+        <v>Configuration Manager</v>
+      </c>
+      <c r="D399" s="5" t="str">
+        <f t="array" ref="D399">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A398)-1, 23)+1, INT((ROW(A398)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E399" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="F399" s="11" t="s">
+        <v>549</v>
+      </c>
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="9"/>
@@ -49757,13 +51757,31 @@
       <c r="Z399" s="9"/>
     </row>
     <row r="400">
-      <c r="A400" s="9"/>
-      <c r="B400" s="9"/>
-      <c r="C400" s="9"/>
-      <c r="D400" s="9"/>
-      <c r="E400" s="9"/>
-      <c r="F400" s="9"/>
-      <c r="G400" s="9"/>
+      <c r="A400" s="5" t="str">
+        <f t="array" ref="A400">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A399)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B400" s="5" t="str">
+        <f t="array" ref="B400">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B399)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C400" s="5" t="str">
+        <f t="array" ref="C400">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A399)-1, 23)+1)</f>
+        <v>Multi-Agent Coordinator</v>
+      </c>
+      <c r="D400" s="5" t="str">
+        <f t="array" ref="D400">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A399)-1, 23)+1, INT((ROW(A399)-1)/23)+1)</f>
+        <v>implicit</v>
+      </c>
+      <c r="E400" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="F400" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="G400" s="11" t="s">
+        <v>552</v>
+      </c>
       <c r="H400" s="9"/>
       <c r="I400" s="9"/>
       <c r="J400" s="9"/>
@@ -49785,10 +51803,23 @@
       <c r="Z400" s="9"/>
     </row>
     <row r="401">
-      <c r="A401" s="9"/>
-      <c r="B401" s="9"/>
-      <c r="C401" s="9"/>
-      <c r="D401" s="9"/>
+      <c r="A401" s="5" t="str">
+        <f t="array" ref="A401">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A400)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B401" s="5" t="str">
+        <f t="array" ref="B401">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B400)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C401" s="5" t="str">
+        <f t="array" ref="C401">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A400)-1, 23)+1)</f>
+        <v>Distributed Execution 
+Coordinator</v>
+      </c>
+      <c r="D401" s="5" t="str">
+        <f t="array" ref="D401">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A400)-1, 23)+1, INT((ROW(A400)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E401" s="9"/>
       <c r="F401" s="9"/>
       <c r="G401" s="9"/>
@@ -49813,13 +51844,31 @@
       <c r="Z401" s="9"/>
     </row>
     <row r="402">
-      <c r="A402" s="9"/>
-      <c r="B402" s="9"/>
-      <c r="C402" s="9"/>
-      <c r="D402" s="9"/>
-      <c r="E402" s="9"/>
-      <c r="F402" s="9"/>
-      <c r="G402" s="9"/>
+      <c r="A402" s="5" t="str">
+        <f t="array" ref="A402">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A401)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B402" s="5" t="str">
+        <f t="array" ref="B402">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B401)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C402" s="5" t="str">
+        <f t="array" ref="C402">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A401)-1, 23)+1)</f>
+        <v>Agent</v>
+      </c>
+      <c r="D402" s="5" t="str">
+        <f t="array" ref="D402">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A401)-1, 23)+1, INT((ROW(A401)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E402" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="F402" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="G402" s="11" t="s">
+        <v>555</v>
+      </c>
       <c r="H402" s="9"/>
       <c r="I402" s="9"/>
       <c r="J402" s="9"/>
@@ -49841,12 +51890,28 @@
       <c r="Z402" s="9"/>
     </row>
     <row r="403">
-      <c r="A403" s="9"/>
-      <c r="B403" s="9"/>
-      <c r="C403" s="9"/>
-      <c r="D403" s="9"/>
-      <c r="E403" s="9"/>
-      <c r="F403" s="9"/>
+      <c r="A403" s="5" t="str">
+        <f t="array" ref="A403">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A402)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B403" s="5" t="str">
+        <f t="array" ref="B403">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B402)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C403" s="5" t="str">
+        <f t="array" ref="C403">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A402)-1, 23)+1)</f>
+        <v>Function Approximator</v>
+      </c>
+      <c r="D403" s="5" t="str">
+        <f t="array" ref="D403">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A402)-1, 23)+1, INT((ROW(A402)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E403" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="F403" s="11" t="s">
+        <v>557</v>
+      </c>
       <c r="G403" s="9"/>
       <c r="H403" s="9"/>
       <c r="I403" s="9"/>
@@ -49869,12 +51934,28 @@
       <c r="Z403" s="9"/>
     </row>
     <row r="404">
-      <c r="A404" s="9"/>
-      <c r="B404" s="9"/>
-      <c r="C404" s="9"/>
-      <c r="D404" s="9"/>
-      <c r="E404" s="9"/>
-      <c r="F404" s="9"/>
+      <c r="A404" s="5" t="str">
+        <f t="array" ref="A404">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A403)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B404" s="5" t="str">
+        <f t="array" ref="B404">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B403)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C404" s="5" t="str">
+        <f t="array" ref="C404">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A403)-1, 23)+1)</f>
+        <v>Buffer</v>
+      </c>
+      <c r="D404" s="5" t="str">
+        <f t="array" ref="D404">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A403)-1, 23)+1, INT((ROW(A403)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E404" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="F404" s="11" t="s">
+        <v>559</v>
+      </c>
       <c r="G404" s="9"/>
       <c r="H404" s="9"/>
       <c r="I404" s="9"/>
@@ -49897,13 +51978,31 @@
       <c r="Z404" s="9"/>
     </row>
     <row r="405">
-      <c r="A405" s="9"/>
-      <c r="B405" s="9"/>
-      <c r="C405" s="9"/>
-      <c r="D405" s="9"/>
-      <c r="E405" s="9"/>
-      <c r="F405" s="9"/>
-      <c r="G405" s="9"/>
+      <c r="A405" s="5" t="str">
+        <f t="array" ref="A405">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A404)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B405" s="5" t="str">
+        <f t="array" ref="B405">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B404)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C405" s="5" t="str">
+        <f t="array" ref="C405">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A404)-1, 23)+1)</f>
+        <v>Learner</v>
+      </c>
+      <c r="D405" s="5" t="str">
+        <f t="array" ref="D405">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A404)-1, 23)+1, INT((ROW(A404)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E405" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="F405" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="G405" s="11" t="s">
+        <v>562</v>
+      </c>
       <c r="H405" s="9"/>
       <c r="I405" s="9"/>
       <c r="J405" s="9"/>
@@ -49925,10 +52024,22 @@
       <c r="Z405" s="9"/>
     </row>
     <row r="406">
-      <c r="A406" s="9"/>
-      <c r="B406" s="9"/>
-      <c r="C406" s="9"/>
-      <c r="D406" s="9"/>
+      <c r="A406" s="5" t="str">
+        <f t="array" ref="A406">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A405)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B406" s="5" t="str">
+        <f t="array" ref="B406">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B405)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C406" s="5" t="str">
+        <f t="array" ref="C406">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A405)-1, 23)+1)</f>
+        <v>Environment</v>
+      </c>
+      <c r="D406" s="5" t="str">
+        <f t="array" ref="D406">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A405)-1, 23)+1, INT((ROW(A405)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E406" s="9"/>
       <c r="F406" s="9"/>
       <c r="G406" s="9"/>
@@ -49953,10 +52064,22 @@
       <c r="Z406" s="9"/>
     </row>
     <row r="407">
-      <c r="A407" s="9"/>
-      <c r="B407" s="9"/>
-      <c r="C407" s="9"/>
-      <c r="D407" s="9"/>
+      <c r="A407" s="5" t="str">
+        <f t="array" ref="A407">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A406)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B407" s="5" t="str">
+        <f t="array" ref="B407">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B406)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C407" s="5" t="str">
+        <f t="array" ref="C407">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A406)-1, 23)+1)</f>
+        <v>Environment Core</v>
+      </c>
+      <c r="D407" s="5" t="str">
+        <f t="array" ref="D407">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A406)-1, 23)+1, INT((ROW(A406)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E407" s="9"/>
       <c r="F407" s="9"/>
       <c r="G407" s="9"/>
@@ -49981,10 +52104,22 @@
       <c r="Z407" s="9"/>
     </row>
     <row r="408">
-      <c r="A408" s="9"/>
-      <c r="B408" s="9"/>
-      <c r="C408" s="9"/>
-      <c r="D408" s="9"/>
+      <c r="A408" s="5" t="str">
+        <f t="array" ref="A408">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A407)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B408" s="5" t="str">
+        <f t="array" ref="B408">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B407)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C408" s="5" t="str">
+        <f t="array" ref="C408">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A407)-1, 23)+1)</f>
+        <v>Simulator</v>
+      </c>
+      <c r="D408" s="5" t="str">
+        <f t="array" ref="D408">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A407)-1, 23)+1, INT((ROW(A407)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E408" s="9"/>
       <c r="F408" s="9"/>
       <c r="G408" s="9"/>
@@ -50009,10 +52144,22 @@
       <c r="Z408" s="9"/>
     </row>
     <row r="409">
-      <c r="A409" s="9"/>
-      <c r="B409" s="9"/>
-      <c r="C409" s="9"/>
-      <c r="D409" s="9"/>
+      <c r="A409" s="5" t="str">
+        <f t="array" ref="A409">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A408)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B409" s="5" t="str">
+        <f t="array" ref="B409">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B408)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C409" s="5" t="str">
+        <f t="array" ref="C409">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A408)-1, 23)+1)</f>
+        <v>Simulator Adapter</v>
+      </c>
+      <c r="D409" s="5" t="str">
+        <f t="array" ref="D409">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A408)-1, 23)+1, INT((ROW(A408)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E409" s="9"/>
       <c r="F409" s="9"/>
       <c r="G409" s="9"/>
@@ -50037,12 +52184,28 @@
       <c r="Z409" s="9"/>
     </row>
     <row r="410">
-      <c r="A410" s="9"/>
-      <c r="B410" s="9"/>
-      <c r="C410" s="9"/>
-      <c r="D410" s="9"/>
-      <c r="E410" s="9"/>
-      <c r="F410" s="9"/>
+      <c r="A410" s="5" t="str">
+        <f t="array" ref="A410">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A409)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B410" s="5" t="str">
+        <f t="array" ref="B410">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B409)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C410" s="5" t="str">
+        <f t="array" ref="C410">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A409)-1, 23)+1)</f>
+        <v>Checkpoint Manager</v>
+      </c>
+      <c r="D410" s="5" t="str">
+        <f t="array" ref="D410">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A409)-1, 23)+1, INT((ROW(A409)-1)/23)+1)</f>
+        <v>explicit</v>
+      </c>
+      <c r="E410" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="F410" s="11" t="s">
+        <v>564</v>
+      </c>
       <c r="G410" s="9"/>
       <c r="H410" s="9"/>
       <c r="I410" s="9"/>
@@ -50065,10 +52228,23 @@
       <c r="Z410" s="9"/>
     </row>
     <row r="411">
-      <c r="A411" s="9"/>
-      <c r="B411" s="9"/>
-      <c r="C411" s="9"/>
-      <c r="D411" s="9"/>
+      <c r="A411" s="5" t="str">
+        <f t="array" ref="A411">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A410)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B411" s="5" t="str">
+        <f t="array" ref="B411">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B410)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C411" s="5" t="str">
+        <f t="array" ref="C411">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A410)-1, 23)+1)</f>
+        <v>Environment Parameter 
+Manager</v>
+      </c>
+      <c r="D411" s="5" t="str">
+        <f t="array" ref="D411">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A410)-1, 23)+1, INT((ROW(A410)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E411" s="9"/>
       <c r="F411" s="9"/>
       <c r="G411" s="9"/>
@@ -50093,10 +52269,22 @@
       <c r="Z411" s="9"/>
     </row>
     <row r="412">
-      <c r="A412" s="9"/>
-      <c r="B412" s="9"/>
-      <c r="C412" s="9"/>
-      <c r="D412" s="9"/>
+      <c r="A412" s="5" t="str">
+        <f t="array" ref="A412">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A411)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B412" s="5" t="str">
+        <f t="array" ref="B412">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B411)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C412" s="5" t="str">
+        <f t="array" ref="C412">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A411)-1, 23)+1)</f>
+        <v>Renderer</v>
+      </c>
+      <c r="D412" s="5" t="str">
+        <f t="array" ref="D412">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A411)-1, 23)+1, INT((ROW(A411)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E412" s="9"/>
       <c r="F412" s="9"/>
       <c r="G412" s="9"/>
@@ -50121,10 +52309,22 @@
       <c r="Z412" s="9"/>
     </row>
     <row r="413">
-      <c r="A413" s="9"/>
-      <c r="B413" s="9"/>
-      <c r="C413" s="9"/>
-      <c r="D413" s="9"/>
+      <c r="A413" s="5" t="str">
+        <f t="array" ref="A413">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A412)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B413" s="5" t="str">
+        <f t="array" ref="B413">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B412)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C413" s="5" t="str">
+        <f t="array" ref="C413">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A412)-1, 23)+1)</f>
+        <v>Recorder</v>
+      </c>
+      <c r="D413" s="5" t="str">
+        <f t="array" ref="D413">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A412)-1, 23)+1, INT((ROW(A412)-1)/23)+1)</f>
+        <v>not implemented</v>
+      </c>
       <c r="E413" s="9"/>
       <c r="F413" s="9"/>
       <c r="G413" s="9"/>
@@ -50149,14 +52349,34 @@
       <c r="Z413" s="9"/>
     </row>
     <row r="414">
-      <c r="A414" s="9"/>
-      <c r="B414" s="9"/>
-      <c r="C414" s="9"/>
-      <c r="D414" s="9"/>
-      <c r="E414" s="9"/>
-      <c r="F414" s="9"/>
-      <c r="G414" s="9"/>
-      <c r="H414" s="9"/>
+      <c r="A414" s="5" t="str">
+        <f t="array" ref="A414">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A413)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B414" s="5" t="str">
+        <f t="array" ref="B414">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B413)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C414" s="5" t="str">
+        <f t="array" ref="C414">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A413)-1, 23)+1)</f>
+        <v>Logger</v>
+      </c>
+      <c r="D414" s="5" t="str">
+        <f t="array" ref="D414">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A413)-1, 23)+1, INT((ROW(A413)-1)/23)+1)</f>
+        <v>external</v>
+      </c>
+      <c r="E414" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="F414" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="G414" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="H414" s="11" t="s">
+        <v>568</v>
+      </c>
       <c r="I414" s="9"/>
       <c r="J414" s="9"/>
       <c r="K414" s="9"/>
@@ -50177,14 +52397,34 @@
       <c r="Z414" s="9"/>
     </row>
     <row r="415">
-      <c r="A415" s="9"/>
-      <c r="B415" s="9"/>
-      <c r="C415" s="9"/>
-      <c r="D415" s="9"/>
-      <c r="E415" s="9"/>
-      <c r="F415" s="9"/>
-      <c r="G415" s="9"/>
-      <c r="H415" s="9"/>
+      <c r="A415" s="5" t="str">
+        <f t="array" ref="A415">INDEX('final-RA-to-framework-summary'!$C$1:$T$1, 1, INT((ROW(A414)-1)/23)+1)</f>
+        <v>F18</v>
+      </c>
+      <c r="B415" s="5" t="str">
+        <f t="array" ref="B415">INDEX('final-RA-to-framework-summary'!$C$2:$T$2, 1, INT((ROW(B414)-1)/23)+1)</f>
+        <v>Tianshou</v>
+      </c>
+      <c r="C415" s="5" t="str">
+        <f t="array" ref="C415">INDEX('final-RA-to-framework-summary'!$B$4:$B$26, MOD(ROW(A414)-1, 23)+1)</f>
+        <v>Reporter</v>
+      </c>
+      <c r="D415" s="5" t="str">
+        <f t="array" ref="D415">INDEX('final-RA-to-framework-summary'!$C$4:$Z$26, MOD(ROW(A414)-1, 23)+1, INT((ROW(A414)-1)/23)+1)</f>
+        <v>external</v>
+      </c>
+      <c r="E415" s="15" t="s">
+        <v>569</v>
+      </c>
+      <c r="F415" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="G415" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="H415" s="11" t="s">
+        <v>571</v>
+      </c>
       <c r="I415" s="9"/>
       <c r="J415" s="9"/>
       <c r="K415" s="9"/>
@@ -66747,44 +68987,95 @@
     <hyperlink r:id="rId103" ref="E253"/>
     <hyperlink r:id="rId104" ref="E254"/>
     <hyperlink r:id="rId105" ref="E256"/>
-    <hyperlink r:id="rId106" ref="E259"/>
-    <hyperlink r:id="rId107" ref="E260"/>
-    <hyperlink r:id="rId108" ref="E261"/>
-    <hyperlink r:id="rId109" ref="E262"/>
-    <hyperlink r:id="rId110" ref="E263"/>
-    <hyperlink r:id="rId111" ref="E264"/>
-    <hyperlink r:id="rId112" ref="E265"/>
-    <hyperlink r:id="rId113" ref="E266"/>
-    <hyperlink r:id="rId114" ref="E267"/>
-    <hyperlink r:id="rId115" ref="E272"/>
-    <hyperlink r:id="rId116" ref="E273"/>
-    <hyperlink r:id="rId117" ref="E277"/>
-    <hyperlink r:id="rId118" ref="E279"/>
-    <hyperlink r:id="rId119" ref="E282"/>
-    <hyperlink r:id="rId120" ref="E283"/>
-    <hyperlink r:id="rId121" ref="E286"/>
-    <hyperlink r:id="rId122" ref="E287"/>
-    <hyperlink r:id="rId123" ref="E288"/>
-    <hyperlink r:id="rId124" ref="E289"/>
-    <hyperlink r:id="rId125" ref="E290"/>
-    <hyperlink r:id="rId126" ref="E295"/>
-    <hyperlink r:id="rId127" ref="E298"/>
-    <hyperlink r:id="rId128" ref="E299"/>
-    <hyperlink r:id="rId129" ref="E302"/>
-    <hyperlink r:id="rId130" ref="E303"/>
-    <hyperlink r:id="rId131" ref="E305"/>
-    <hyperlink r:id="rId132" ref="E306"/>
-    <hyperlink r:id="rId133" ref="E307"/>
-    <hyperlink r:id="rId134" ref="E308"/>
-    <hyperlink r:id="rId135" ref="E309"/>
-    <hyperlink r:id="rId136" ref="E310"/>
-    <hyperlink r:id="rId137" ref="E311"/>
-    <hyperlink r:id="rId138" ref="E312"/>
-    <hyperlink r:id="rId139" ref="E313"/>
-    <hyperlink r:id="rId140" ref="E318"/>
-    <hyperlink r:id="rId141" ref="E322"/>
-    <hyperlink r:id="rId142" ref="E323"/>
+    <hyperlink r:id="rId106" ref="E257"/>
+    <hyperlink r:id="rId107" ref="E259"/>
+    <hyperlink r:id="rId108" ref="E260"/>
+    <hyperlink r:id="rId109" ref="E261"/>
+    <hyperlink r:id="rId110" ref="E262"/>
+    <hyperlink r:id="rId111" ref="E263"/>
+    <hyperlink r:id="rId112" ref="E264"/>
+    <hyperlink r:id="rId113" ref="E265"/>
+    <hyperlink r:id="rId114" ref="E266"/>
+    <hyperlink r:id="rId115" ref="E267"/>
+    <hyperlink r:id="rId116" ref="E272"/>
+    <hyperlink r:id="rId117" ref="E273"/>
+    <hyperlink r:id="rId118" ref="E277"/>
+    <hyperlink r:id="rId119" ref="E279"/>
+    <hyperlink r:id="rId120" ref="E282"/>
+    <hyperlink r:id="rId121" ref="E283"/>
+    <hyperlink r:id="rId122" ref="E286"/>
+    <hyperlink r:id="rId123" ref="E287"/>
+    <hyperlink r:id="rId124" ref="E288"/>
+    <hyperlink r:id="rId125" ref="E289"/>
+    <hyperlink r:id="rId126" ref="E290"/>
+    <hyperlink r:id="rId127" ref="E295"/>
+    <hyperlink r:id="rId128" ref="E298"/>
+    <hyperlink r:id="rId129" ref="E299"/>
+    <hyperlink r:id="rId130" ref="E302"/>
+    <hyperlink r:id="rId131" ref="E303"/>
+    <hyperlink r:id="rId132" ref="E305"/>
+    <hyperlink r:id="rId133" ref="E306"/>
+    <hyperlink r:id="rId134" ref="E307"/>
+    <hyperlink r:id="rId135" ref="E308"/>
+    <hyperlink r:id="rId136" ref="E309"/>
+    <hyperlink r:id="rId137" ref="E310"/>
+    <hyperlink r:id="rId138" ref="E311"/>
+    <hyperlink r:id="rId139" ref="E312"/>
+    <hyperlink r:id="rId140" ref="E313"/>
+    <hyperlink r:id="rId141" ref="E318"/>
+    <hyperlink r:id="rId142" ref="E322"/>
+    <hyperlink r:id="rId143" ref="E323"/>
+    <hyperlink r:id="rId144" ref="E325"/>
+    <hyperlink r:id="rId145" ref="E327"/>
+    <hyperlink r:id="rId146" ref="E328"/>
+    <hyperlink r:id="rId147" ref="E329"/>
+    <hyperlink r:id="rId148" ref="E330"/>
+    <hyperlink r:id="rId149" ref="E331"/>
+    <hyperlink r:id="rId150" ref="E333"/>
+    <hyperlink r:id="rId151" ref="E334"/>
+    <hyperlink r:id="rId152" ref="E335"/>
+    <hyperlink r:id="rId153" ref="E336"/>
+    <hyperlink r:id="rId154" ref="E341"/>
+    <hyperlink r:id="rId155" ref="E344"/>
+    <hyperlink r:id="rId156" ref="E345"/>
+    <hyperlink r:id="rId157" ref="E346"/>
+    <hyperlink r:id="rId158" ref="E348"/>
+    <hyperlink r:id="rId159" ref="E351"/>
+    <hyperlink r:id="rId160" ref="E352"/>
+    <hyperlink r:id="rId161" ref="E353"/>
+    <hyperlink r:id="rId162" ref="E355"/>
+    <hyperlink r:id="rId163" ref="E356"/>
+    <hyperlink r:id="rId164" ref="E357"/>
+    <hyperlink r:id="rId165" ref="E358"/>
+    <hyperlink r:id="rId166" ref="E359"/>
+    <hyperlink r:id="rId167" ref="E364"/>
+    <hyperlink r:id="rId168" ref="E368"/>
+    <hyperlink r:id="rId169" ref="E369"/>
+    <hyperlink r:id="rId170" ref="E371"/>
+    <hyperlink r:id="rId171" ref="E374"/>
+    <hyperlink r:id="rId172" ref="E375"/>
+    <hyperlink r:id="rId173" ref="E376"/>
+    <hyperlink r:id="rId174" ref="E379"/>
+    <hyperlink r:id="rId175" ref="E380"/>
+    <hyperlink r:id="rId176" ref="E381"/>
+    <hyperlink r:id="rId177" ref="E382"/>
+    <hyperlink r:id="rId178" ref="E387"/>
+    <hyperlink r:id="rId179" ref="E390"/>
+    <hyperlink r:id="rId180" ref="E391"/>
+    <hyperlink r:id="rId181" ref="E392"/>
+    <hyperlink r:id="rId182" ref="E394"/>
+    <hyperlink r:id="rId183" ref="E397"/>
+    <hyperlink r:id="rId184" ref="E398"/>
+    <hyperlink r:id="rId185" ref="E399"/>
+    <hyperlink r:id="rId186" ref="E400"/>
+    <hyperlink r:id="rId187" ref="E402"/>
+    <hyperlink r:id="rId188" ref="E403"/>
+    <hyperlink r:id="rId189" ref="E404"/>
+    <hyperlink r:id="rId190" ref="E405"/>
+    <hyperlink r:id="rId191" ref="E410"/>
+    <hyperlink r:id="rId192" ref="E414"/>
+    <hyperlink r:id="rId193" ref="E415"/>
   </hyperlinks>
-  <drawing r:id="rId143"/>
+  <drawing r:id="rId194"/>
 </worksheet>
 </file>